--- a/investment-engine/sector/AI/stock-data/investment_data_06172026.xlsx
+++ b/investment-engine/sector/AI/stock-data/investment_data_06172026.xlsx
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>208.35</v>
+        <v>206.22</v>
       </c>
       <c r="D2" t="n">
-        <v>48.17</v>
+        <v>46.48</v>
       </c>
       <c r="E2" t="n">
-        <v>31.91</v>
+        <v>31.58</v>
       </c>
       <c r="F2" t="n">
-        <v>19.89</v>
+        <v>19.69</v>
       </c>
       <c r="G2" t="n">
-        <v>5042064980000</v>
+        <v>4990524030000</v>
       </c>
       <c r="H2" t="n">
-        <v>166.68</v>
+        <v>164.98</v>
       </c>
       <c r="I2" t="n">
         <v>309.93</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>48.75</v>
+        <v>50.29</v>
       </c>
       <c r="L2" t="n">
         <v>85.23</v>
@@ -609,7 +609,7 @@
         <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="3">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.63</v>
+        <v>29.13</v>
       </c>
       <c r="D3" t="n">
-        <v>40.54</v>
+        <v>39.66</v>
       </c>
       <c r="E3" t="n">
-        <v>15.63</v>
+        <v>15.37</v>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>19165170000</v>
+        <v>18843410000</v>
       </c>
       <c r="H3" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="I3" t="n">
         <v>35.87</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>21.06</v>
+        <v>23.14</v>
       </c>
       <c r="L3" t="n">
         <v>122.68</v>
@@ -678,7 +678,7 @@
         <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1053.32</v>
+        <v>1044.82</v>
       </c>
       <c r="D4" t="n">
-        <v>62.28</v>
+        <v>61.83</v>
       </c>
       <c r="E4" t="n">
-        <v>49.73</v>
+        <v>49.33</v>
       </c>
       <c r="F4" t="n">
-        <v>20.44</v>
+        <v>20.27</v>
       </c>
       <c r="G4" t="n">
-        <v>1187867070000</v>
+        <v>1178278580000</v>
       </c>
       <c r="H4" t="n">
-        <v>842.66</v>
+        <v>835.86</v>
       </c>
       <c r="I4" t="n">
         <v>954.52</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.380000000000001</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>196.29</v>
@@ -747,7 +747,7 @@
         <v>1.35</v>
       </c>
       <c r="U4" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -762,22 +762,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>390.23</v>
+        <v>385.45</v>
       </c>
       <c r="D5" t="n">
-        <v>38.67</v>
+        <v>36.84</v>
       </c>
       <c r="E5" t="n">
-        <v>23.24</v>
+        <v>22.96</v>
       </c>
       <c r="F5" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>2898798110000</v>
+        <v>2863327150000</v>
       </c>
       <c r="H5" t="n">
-        <v>312.18</v>
+        <v>308.36</v>
       </c>
       <c r="I5" t="n">
         <v>559.29</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>43.32</v>
+        <v>45.1</v>
       </c>
       <c r="L5" t="n">
         <v>18.3</v>
@@ -816,211 +816,211 @@
         <v>1.23</v>
       </c>
       <c r="U5" t="n">
-        <v>63.9</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLAB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30.91</v>
+        <v>363.82</v>
       </c>
       <c r="D6" t="n">
-        <v>36.3</v>
+        <v>46.11</v>
       </c>
       <c r="E6" t="n">
-        <v>11.32</v>
+        <v>27.75</v>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>10.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1822570000</v>
+        <v>4396650510000</v>
       </c>
       <c r="H6" t="n">
-        <v>24.73</v>
+        <v>291.06</v>
       </c>
       <c r="I6" t="n">
-        <v>43</v>
+        <v>433.97</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>39.11</v>
+        <v>19.28</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5</v>
+        <v>22.34</v>
       </c>
       <c r="M6" t="n">
-        <v>268.2</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>33.77</v>
+        <v>60.43</v>
       </c>
       <c r="O6" t="n">
-        <v>18.47</v>
+        <v>37.86</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R6" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.38</v>
       </c>
-      <c r="R6" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="S6" t="n">
-        <v>95.68000000000001</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" t="n">
-        <v>63.8</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>PLAB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>246.83</v>
+        <v>31.76</v>
       </c>
       <c r="D7" t="n">
-        <v>59.61</v>
+        <v>38.41</v>
       </c>
       <c r="E7" t="n">
-        <v>99.54000000000001</v>
+        <v>11.63</v>
       </c>
       <c r="F7" t="n">
-        <v>34.48</v>
+        <v>2.17</v>
       </c>
       <c r="G7" t="n">
-        <v>46028340000</v>
+        <v>1872690000</v>
       </c>
       <c r="H7" t="n">
-        <v>197.46</v>
+        <v>25.41</v>
       </c>
       <c r="I7" t="n">
-        <v>266.44</v>
+        <v>43</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>7.94</v>
+        <v>35.39</v>
       </c>
       <c r="L7" t="n">
-        <v>157.02</v>
+        <v>-0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>336.83</v>
+        <v>268.2</v>
       </c>
       <c r="N7" t="n">
-        <v>68.01000000000001</v>
+        <v>33.77</v>
       </c>
       <c r="O7" t="n">
-        <v>35.37</v>
+        <v>18.47</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.23</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
-        <v>10.3</v>
+        <v>4.06</v>
       </c>
       <c r="S7" t="n">
-        <v>75.22</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>371.07</v>
+        <v>258.58</v>
       </c>
       <c r="D8" t="n">
-        <v>50.88</v>
+        <v>62.46</v>
       </c>
       <c r="E8" t="n">
-        <v>28.31</v>
+        <v>104.27</v>
       </c>
       <c r="F8" t="n">
-        <v>10.6</v>
+        <v>36.12</v>
       </c>
       <c r="G8" t="n">
-        <v>4484264480000</v>
+        <v>48218520000</v>
       </c>
       <c r="H8" t="n">
-        <v>296.86</v>
+        <v>206.86</v>
       </c>
       <c r="I8" t="n">
-        <v>433.97</v>
+        <v>266.44</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16.95</v>
+        <v>3.04</v>
       </c>
       <c r="L8" t="n">
-        <v>22.34</v>
+        <v>157.02</v>
       </c>
       <c r="M8" t="n">
-        <v>81.95999999999999</v>
+        <v>336.83</v>
       </c>
       <c r="N8" t="n">
-        <v>60.43</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>37.86</v>
+        <v>35.37</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.24</v>
+        <v>3.23</v>
       </c>
       <c r="R8" t="n">
-        <v>52.1</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>38.87</v>
+        <v>75.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="U8" t="n">
         <v>61.9</v>
@@ -1029,139 +1029,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>387.6</v>
+        <v>851.9</v>
       </c>
       <c r="D9" t="n">
-        <v>44.57</v>
+        <v>54.67</v>
       </c>
       <c r="E9" t="n">
-        <v>64.52</v>
+        <v>76.16</v>
       </c>
       <c r="F9" t="n">
-        <v>24.44</v>
+        <v>9.06</v>
       </c>
       <c r="G9" t="n">
-        <v>1844038070000</v>
+        <v>26141360000</v>
       </c>
       <c r="H9" t="n">
-        <v>310.08</v>
+        <v>681.52</v>
       </c>
       <c r="I9" t="n">
-        <v>524.1799999999999</v>
+        <v>956.4299999999999</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>35.24</v>
+        <v>12.27</v>
       </c>
       <c r="L9" t="n">
-        <v>47.87</v>
+        <v>91.59</v>
       </c>
       <c r="M9" t="n">
-        <v>85.59</v>
+        <v>141.86</v>
       </c>
       <c r="N9" t="n">
-        <v>65.66</v>
+        <v>22.43</v>
       </c>
       <c r="O9" t="n">
-        <v>38.85</v>
+        <v>12.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="S9" t="n">
-        <v>78.68000000000001</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STRL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>861.1</v>
+        <v>240.2</v>
       </c>
       <c r="D10" t="n">
-        <v>55.63</v>
+        <v>38.69</v>
       </c>
       <c r="E10" t="n">
-        <v>76.98</v>
+        <v>28.71</v>
       </c>
       <c r="F10" t="n">
-        <v>9.16</v>
+        <v>3.48</v>
       </c>
       <c r="G10" t="n">
-        <v>26423670000</v>
+        <v>2583857640000</v>
       </c>
       <c r="H10" t="n">
-        <v>688.88</v>
+        <v>192.16</v>
       </c>
       <c r="I10" t="n">
-        <v>956.4299999999999</v>
+        <v>316.56</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>11.07</v>
+        <v>31.79</v>
       </c>
       <c r="L10" t="n">
-        <v>91.59</v>
+        <v>16.61</v>
       </c>
       <c r="M10" t="n">
-        <v>141.86</v>
+        <v>75.33</v>
       </c>
       <c r="N10" t="n">
-        <v>22.43</v>
+        <v>50.6</v>
       </c>
       <c r="O10" t="n">
-        <v>12.02</v>
+        <v>12.22</v>
       </c>
       <c r="P10" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="R10" t="n">
-        <v>2.43</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>93.26000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="U10" t="n">
-        <v>60.7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -1176,28 +1176,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>407.84</v>
+        <v>414.4</v>
       </c>
       <c r="D11" t="n">
-        <v>65.75</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>32.41</v>
+        <v>32.93</v>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>264325840000</v>
+        <v>268579180000</v>
       </c>
       <c r="H11" t="n">
-        <v>326.27</v>
+        <v>331.52</v>
       </c>
       <c r="I11" t="n">
         <v>496.76</v>
       </c>
       <c r="K11" t="n">
-        <v>21.8</v>
+        <v>19.87</v>
       </c>
       <c r="L11" t="n">
         <v>87.48999999999999</v>
@@ -1224,76 +1224,76 @@
         <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>246.71</v>
+        <v>397.83</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>47.53</v>
       </c>
       <c r="E12" t="n">
-        <v>29.48</v>
+        <v>66.23</v>
       </c>
       <c r="F12" t="n">
-        <v>3.57</v>
+        <v>25.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2653886530000</v>
+        <v>1892707580000</v>
       </c>
       <c r="H12" t="n">
-        <v>197.37</v>
+        <v>318.26</v>
       </c>
       <c r="I12" t="n">
-        <v>316.56</v>
+        <v>524.1799999999999</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>28.31</v>
+        <v>31.76</v>
       </c>
       <c r="L12" t="n">
-        <v>16.61</v>
+        <v>47.87</v>
       </c>
       <c r="M12" t="n">
-        <v>75.33</v>
+        <v>85.59</v>
       </c>
       <c r="N12" t="n">
-        <v>50.6</v>
+        <v>65.66</v>
       </c>
       <c r="O12" t="n">
-        <v>12.22</v>
+        <v>38.85</v>
       </c>
       <c r="P12" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="Q12" t="n">
         <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>8.949999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="S12" t="n">
-        <v>66.63</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="13">
@@ -1308,22 +1308,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>432.3</v>
+        <v>436.29</v>
       </c>
       <c r="D13" t="n">
-        <v>55.28</v>
+        <v>56.49</v>
       </c>
       <c r="E13" t="n">
-        <v>35.93</v>
+        <v>36.26</v>
       </c>
       <c r="F13" t="n">
-        <v>16.87</v>
+        <v>17.03</v>
       </c>
       <c r="G13" t="n">
-        <v>2242115240000</v>
+        <v>2262809400000</v>
       </c>
       <c r="H13" t="n">
-        <v>345.84</v>
+        <v>349.03</v>
       </c>
       <c r="I13" t="n">
         <v>460.4</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>6.5</v>
+        <v>5.53</v>
       </c>
       <c r="L13" t="n">
         <v>40.49</v>
@@ -1362,208 +1362,208 @@
         <v>1.21</v>
       </c>
       <c r="U13" t="n">
-        <v>59.3</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>268.7</v>
+        <v>342.39</v>
       </c>
       <c r="D14" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="E14" t="n">
-        <v>23.33</v>
+        <v>52.47</v>
       </c>
       <c r="F14" t="n">
-        <v>3.41</v>
+        <v>10.58</v>
       </c>
       <c r="G14" t="n">
-        <v>97051780000</v>
+        <v>27539090000</v>
       </c>
       <c r="H14" t="n">
-        <v>214.96</v>
+        <v>273.91</v>
       </c>
       <c r="I14" t="n">
-        <v>365.11</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
+        <v>399.82</v>
       </c>
       <c r="K14" t="n">
-        <v>35.88</v>
+        <v>16.77</v>
       </c>
       <c r="L14" t="n">
-        <v>23.45</v>
+        <v>25.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1095.18</v>
+        <v>111.72</v>
       </c>
       <c r="N14" t="n">
-        <v>13.18</v>
+        <v>71.67</v>
       </c>
       <c r="O14" t="n">
-        <v>13.3</v>
+        <v>-1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
-        <v>6.48</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
-        <v>73.70999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="T14" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="U14" t="n">
-        <v>58.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>882</v>
+        <v>271.38</v>
       </c>
       <c r="D15" t="n">
-        <v>48.31</v>
+        <v>50.07</v>
       </c>
       <c r="E15" t="n">
-        <v>163.69</v>
+        <v>23.57</v>
       </c>
       <c r="F15" t="n">
-        <v>27.58</v>
+        <v>3.44</v>
       </c>
       <c r="G15" t="n">
-        <v>68619600000</v>
+        <v>98020190000</v>
       </c>
       <c r="H15" t="n">
-        <v>705.6</v>
+        <v>217.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1132.81</v>
+        <v>365.11</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>28.44</v>
+        <v>34.54</v>
       </c>
       <c r="L15" t="n">
-        <v>90.12</v>
+        <v>23.45</v>
       </c>
       <c r="M15" t="n">
-        <v>332.76</v>
+        <v>1095.18</v>
       </c>
       <c r="N15" t="n">
-        <v>35.36</v>
+        <v>13.18</v>
       </c>
       <c r="O15" t="n">
-        <v>17.61</v>
+        <v>13.3</v>
       </c>
       <c r="P15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.48</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.57</v>
+        <v>6.48</v>
       </c>
       <c r="S15" t="n">
-        <v>102.92</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="U15" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>346.92</v>
+        <v>877.04</v>
       </c>
       <c r="D16" t="n">
-        <v>53.87</v>
+        <v>47.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>162.77</v>
       </c>
       <c r="F16" t="n">
-        <v>10.72</v>
+        <v>27.42</v>
       </c>
       <c r="G16" t="n">
-        <v>27903440000</v>
+        <v>68233710000</v>
       </c>
       <c r="H16" t="n">
-        <v>277.54</v>
+        <v>701.63</v>
       </c>
       <c r="I16" t="n">
-        <v>399.82</v>
+        <v>1132.81</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>15.25</v>
+        <v>29.16</v>
       </c>
       <c r="L16" t="n">
-        <v>25.25</v>
+        <v>90.12</v>
       </c>
       <c r="M16" t="n">
-        <v>111.72</v>
+        <v>332.76</v>
       </c>
       <c r="N16" t="n">
-        <v>71.67</v>
+        <v>35.36</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.12</v>
+        <v>17.61</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>4.01</v>
+        <v>2.57</v>
       </c>
       <c r="S16" t="n">
-        <v>90.63</v>
+        <v>102.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="U16" t="n">
-        <v>57.6</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="17">
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1927.03</v>
+        <v>1945.03</v>
       </c>
       <c r="D17" t="n">
-        <v>55.82</v>
+        <v>56.99</v>
       </c>
       <c r="E17" t="n">
-        <v>55.62</v>
+        <v>56.14</v>
       </c>
       <c r="F17" t="n">
-        <v>6.69</v>
+        <v>6.76</v>
       </c>
       <c r="G17" t="n">
-        <v>67836130000</v>
+        <v>68469780000</v>
       </c>
       <c r="H17" t="n">
-        <v>1541.62</v>
+        <v>1556.02</v>
       </c>
       <c r="I17" t="n">
         <v>2115.29</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>9.77</v>
+        <v>8.75</v>
       </c>
       <c r="L17" t="n">
         <v>56.47</v>
@@ -1632,490 +1632,490 @@
         <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>57.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>992.3</v>
+        <v>384.88</v>
       </c>
       <c r="D18" t="n">
-        <v>52.23</v>
+        <v>65.42</v>
       </c>
       <c r="E18" t="n">
-        <v>28.91</v>
+        <v>259.42</v>
       </c>
       <c r="F18" t="n">
-        <v>6.78</v>
+        <v>65.88</v>
       </c>
       <c r="G18" t="n">
-        <v>266650860000</v>
+        <v>65970640000</v>
       </c>
       <c r="H18" t="n">
-        <v>793.84</v>
+        <v>307.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1240.22</v>
+        <v>253.06</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>24.98</v>
+        <v>-34.25</v>
       </c>
       <c r="L18" t="n">
-        <v>15.98</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>1816.17</v>
+        <v>148.21</v>
       </c>
       <c r="N18" t="n">
-        <v>20.16</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>23.83</v>
+        <v>26.72</v>
       </c>
       <c r="P18" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.08</v>
+        <v>3.93</v>
       </c>
       <c r="R18" t="n">
-        <v>0.15</v>
+        <v>18.28</v>
       </c>
       <c r="S18" t="n">
-        <v>78.51000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>215.31</v>
+        <v>1016.18</v>
       </c>
       <c r="D19" t="n">
-        <v>55.8</v>
+        <v>55.58</v>
       </c>
       <c r="E19" t="n">
-        <v>34.75</v>
+        <v>29.61</v>
       </c>
       <c r="F19" t="n">
-        <v>3.69</v>
+        <v>6.94</v>
       </c>
       <c r="G19" t="n">
-        <v>55313140000</v>
+        <v>273069240000</v>
       </c>
       <c r="H19" t="n">
-        <v>172.25</v>
+        <v>812.9400000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>265.37</v>
+        <v>1227.4</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>23.25</v>
+        <v>20.79</v>
       </c>
       <c r="L19" t="n">
-        <v>27.65</v>
+        <v>15.98</v>
       </c>
       <c r="M19" t="n">
-        <v>16.52</v>
+        <v>1816.17</v>
       </c>
       <c r="N19" t="n">
-        <v>90.81999999999999</v>
+        <v>20.16</v>
       </c>
       <c r="O19" t="n">
-        <v>10.76</v>
+        <v>23.83</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.52</v>
+        <v>1.08</v>
       </c>
       <c r="R19" t="n">
-        <v>1.92</v>
+        <v>0.15</v>
       </c>
       <c r="S19" t="n">
-        <v>92.40000000000001</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>57.1</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>372.45</v>
+        <v>219.62</v>
       </c>
       <c r="D20" t="n">
-        <v>63.54</v>
+        <v>60.64</v>
       </c>
       <c r="E20" t="n">
-        <v>251.04</v>
+        <v>35.44</v>
       </c>
       <c r="F20" t="n">
-        <v>63.75</v>
+        <v>3.77</v>
       </c>
       <c r="G20" t="n">
-        <v>63840890000</v>
+        <v>56420480000</v>
       </c>
       <c r="H20" t="n">
-        <v>297.96</v>
+        <v>175.7</v>
       </c>
       <c r="I20" t="n">
-        <v>253.06</v>
+        <v>265.37</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-32.06</v>
+        <v>20.83</v>
       </c>
       <c r="L20" t="n">
-        <v>93.40000000000001</v>
+        <v>27.65</v>
       </c>
       <c r="M20" t="n">
-        <v>148.21</v>
+        <v>16.52</v>
       </c>
       <c r="N20" t="n">
-        <v>75.98999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>26.72</v>
+        <v>10.76</v>
       </c>
       <c r="P20" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.93</v>
+        <v>0.52</v>
       </c>
       <c r="R20" t="n">
-        <v>18.28</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>71.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>56.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48.52</v>
+        <v>101</v>
       </c>
       <c r="D21" t="n">
-        <v>63.2</v>
+        <v>45.42</v>
       </c>
       <c r="E21" t="n">
-        <v>46.52</v>
+        <v>60.08</v>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>7.46</v>
       </c>
       <c r="G21" t="n">
-        <v>64250360000</v>
+        <v>104162110000</v>
       </c>
       <c r="H21" t="n">
-        <v>38.82</v>
+        <v>80.8</v>
       </c>
       <c r="I21" t="n">
-        <v>68.59</v>
+        <v>140.76</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>41.36</v>
+        <v>39.37</v>
       </c>
       <c r="L21" t="n">
-        <v>40.64</v>
+        <v>22.09</v>
       </c>
       <c r="M21" t="n">
-        <v>150.91</v>
+        <v>2.64</v>
       </c>
       <c r="N21" t="n">
-        <v>31.36</v>
+        <v>76.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>12.59</v>
       </c>
       <c r="P21" t="n">
-        <v>0.84</v>
+        <v>0.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.43</v>
+        <v>0.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0.38</v>
+        <v>0.91</v>
       </c>
       <c r="S21" t="n">
-        <v>92.45</v>
+        <v>86.27</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="U21" t="n">
-        <v>55.9</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>302.49</v>
+        <v>188.04</v>
       </c>
       <c r="D22" t="n">
-        <v>45.34</v>
+        <v>44.6</v>
       </c>
       <c r="E22" t="n">
-        <v>75.94</v>
+        <v>32.28</v>
       </c>
       <c r="F22" t="n">
-        <v>10.72</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>116189080000</v>
+        <v>540826050000</v>
       </c>
       <c r="H22" t="n">
-        <v>241.99</v>
+        <v>150.43</v>
       </c>
       <c r="I22" t="n">
-        <v>380.63</v>
+        <v>255.38</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>25.83</v>
+        <v>35.81</v>
       </c>
       <c r="L22" t="n">
-        <v>30.13</v>
+        <v>20.63</v>
       </c>
       <c r="M22" t="n">
-        <v>135.9</v>
+        <v>21.47</v>
       </c>
       <c r="N22" t="n">
-        <v>35</v>
+        <v>73.55</v>
       </c>
       <c r="O22" t="n">
-        <v>14.37</v>
+        <v>25.21</v>
       </c>
       <c r="P22" t="n">
-        <v>0.77</v>
+        <v>3.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.71</v>
+        <v>40.54</v>
       </c>
       <c r="S22" t="n">
-        <v>84.73</v>
+        <v>43.83</v>
       </c>
       <c r="T22" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>55.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>186.92</v>
+        <v>50.06</v>
       </c>
       <c r="D23" t="n">
-        <v>44.09</v>
+        <v>65.56</v>
       </c>
       <c r="E23" t="n">
-        <v>32.08</v>
+        <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>7.98</v>
+        <v>1.7</v>
       </c>
       <c r="G23" t="n">
-        <v>537590490000</v>
+        <v>66296250000</v>
       </c>
       <c r="H23" t="n">
-        <v>149.54</v>
+        <v>40.05</v>
       </c>
       <c r="I23" t="n">
-        <v>255.38</v>
+        <v>68.59</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>36.63</v>
+        <v>37.02</v>
       </c>
       <c r="L23" t="n">
-        <v>20.63</v>
+        <v>40.64</v>
       </c>
       <c r="M23" t="n">
-        <v>21.47</v>
+        <v>150.91</v>
       </c>
       <c r="N23" t="n">
-        <v>73.55</v>
+        <v>31.36</v>
       </c>
       <c r="O23" t="n">
-        <v>25.21</v>
+        <v>3.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.63</v>
+        <v>0.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>40.54</v>
+        <v>0.38</v>
       </c>
       <c r="S23" t="n">
-        <v>43.83</v>
+        <v>92.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100.73</v>
+        <v>315.26</v>
       </c>
       <c r="D24" t="n">
-        <v>45.19</v>
+        <v>50.53</v>
       </c>
       <c r="E24" t="n">
-        <v>59.92</v>
+        <v>79.14</v>
       </c>
       <c r="F24" t="n">
-        <v>7.44</v>
+        <v>11.17</v>
       </c>
       <c r="G24" t="n">
-        <v>103883660000</v>
+        <v>121093920000</v>
       </c>
       <c r="H24" t="n">
-        <v>80.58</v>
+        <v>252.21</v>
       </c>
       <c r="I24" t="n">
-        <v>140.76</v>
+        <v>380.63</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>39.74</v>
+        <v>20.74</v>
       </c>
       <c r="L24" t="n">
-        <v>22.09</v>
+        <v>30.13</v>
       </c>
       <c r="M24" t="n">
-        <v>2.64</v>
+        <v>135.9</v>
       </c>
       <c r="N24" t="n">
-        <v>76.56</v>
+        <v>35</v>
       </c>
       <c r="O24" t="n">
-        <v>12.59</v>
+        <v>14.37</v>
       </c>
       <c r="P24" t="n">
-        <v>0.21</v>
+        <v>0.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.95</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>0.91</v>
+        <v>1.71</v>
       </c>
       <c r="S24" t="n">
-        <v>86.27</v>
+        <v>84.73</v>
       </c>
       <c r="T24" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="U24" t="n">
-        <v>55.3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>126.2</v>
+        <v>126.15</v>
       </c>
       <c r="D25" t="n">
-        <v>41.1</v>
+        <v>41.07</v>
       </c>
       <c r="F25" t="n">
         <v>6.43</v>
       </c>
       <c r="G25" t="n">
-        <v>20407740000</v>
+        <v>20400460000</v>
       </c>
       <c r="H25" t="n">
-        <v>100.96</v>
+        <v>100.92</v>
       </c>
       <c r="I25" t="n">
         <v>192.67</v>
       </c>
       <c r="K25" t="n">
-        <v>52.67</v>
+        <v>52.73</v>
       </c>
       <c r="L25" t="n">
         <v>25.43</v>
@@ -2184,685 +2184,685 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>693.5700000000001</v>
+        <v>167.95</v>
       </c>
       <c r="D26" t="n">
-        <v>74.42</v>
+        <v>58.35</v>
       </c>
       <c r="E26" t="n">
-        <v>41.4</v>
+        <v>57.51</v>
       </c>
       <c r="F26" t="n">
-        <v>20.3</v>
+        <v>21.78</v>
       </c>
       <c r="G26" t="n">
-        <v>239059460000</v>
+        <v>211483080000</v>
       </c>
       <c r="H26" t="n">
-        <v>554.86</v>
+        <v>134.36</v>
       </c>
       <c r="I26" t="n">
-        <v>560</v>
+        <v>189.42</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-19.26</v>
+        <v>12.78</v>
       </c>
       <c r="L26" t="n">
-        <v>45.47</v>
+        <v>35.13</v>
       </c>
       <c r="M26" t="n">
-        <v>483.37</v>
+        <v>26.22</v>
       </c>
       <c r="N26" t="n">
-        <v>45.39</v>
+        <v>63.54</v>
       </c>
       <c r="O26" t="n">
-        <v>54.28</v>
+        <v>38.32</v>
       </c>
       <c r="P26" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0.95</v>
+        <v>17.07</v>
       </c>
       <c r="S26" t="n">
-        <v>97.73999999999999</v>
+        <v>72.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="U26" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>168.71</v>
+        <v>45.53</v>
       </c>
       <c r="D27" t="n">
-        <v>58.9</v>
+        <v>52.25</v>
       </c>
       <c r="E27" t="n">
-        <v>57.77</v>
+        <v>18.89</v>
       </c>
       <c r="F27" t="n">
-        <v>21.88</v>
+        <v>2.17</v>
       </c>
       <c r="G27" t="n">
-        <v>212440090000</v>
+        <v>2252140000</v>
       </c>
       <c r="H27" t="n">
-        <v>134.97</v>
+        <v>36.42</v>
       </c>
       <c r="I27" t="n">
-        <v>189.42</v>
+        <v>59</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>12.28</v>
+        <v>29.58</v>
       </c>
       <c r="L27" t="n">
-        <v>35.13</v>
+        <v>11.04</v>
       </c>
       <c r="M27" t="n">
-        <v>26.22</v>
+        <v>-10.25</v>
       </c>
       <c r="N27" t="n">
-        <v>63.54</v>
+        <v>62.66</v>
       </c>
       <c r="O27" t="n">
-        <v>38.32</v>
+        <v>12.36</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
-        <v>17.07</v>
+        <v>5.93</v>
       </c>
       <c r="S27" t="n">
-        <v>72.05</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.12</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>52.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>267.74</v>
+        <v>832.59</v>
       </c>
       <c r="D28" t="n">
-        <v>65.84</v>
+        <v>47.98</v>
       </c>
       <c r="E28" t="n">
-        <v>89.33</v>
+        <v>27.86</v>
       </c>
       <c r="F28" t="n">
-        <v>76.75</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>67376880000</v>
+        <v>37000530000</v>
       </c>
       <c r="H28" t="n">
-        <v>214.19</v>
+        <v>666.0700000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>255.29</v>
+        <v>1000.14</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.65</v>
+        <v>20.12</v>
       </c>
       <c r="L28" t="n">
-        <v>621.52</v>
+        <v>19.67</v>
       </c>
       <c r="M28" t="n">
-        <v>521.4</v>
+        <v>30.04</v>
       </c>
       <c r="N28" t="n">
-        <v>7.48</v>
+        <v>19.29</v>
       </c>
       <c r="O28" t="n">
-        <v>95.27</v>
+        <v>7.54</v>
       </c>
       <c r="P28" t="n">
-        <v>1.31</v>
+        <v>0.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.28</v>
+        <v>1.13</v>
       </c>
       <c r="R28" t="n">
-        <v>19.73</v>
+        <v>0.74</v>
       </c>
       <c r="S28" t="n">
-        <v>50.26</v>
+        <v>96.41</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U28" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>409.8</v>
+        <v>293.24</v>
       </c>
       <c r="D29" t="n">
-        <v>63.25</v>
+        <v>57.12</v>
+      </c>
+      <c r="E29" t="n">
+        <v>131</v>
       </c>
       <c r="F29" t="n">
-        <v>3.99</v>
+        <v>4.87</v>
       </c>
       <c r="G29" t="n">
-        <v>18602880000</v>
+        <v>15487700000</v>
       </c>
       <c r="H29" t="n">
-        <v>327.84</v>
+        <v>234.59</v>
       </c>
       <c r="I29" t="n">
-        <v>478.62</v>
+        <v>351.75</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>16.79</v>
+        <v>19.95</v>
       </c>
       <c r="L29" t="n">
-        <v>21.64</v>
+        <v>47.47</v>
       </c>
       <c r="M29" t="n">
-        <v>145.11</v>
+        <v>47.51</v>
       </c>
       <c r="N29" t="n">
-        <v>63.43</v>
+        <v>23.19</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.45</v>
+        <v>3.82</v>
       </c>
       <c r="P29" t="n">
-        <v>6.34</v>
+        <v>0.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="R29" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>103.78</v>
+        <v>106.36</v>
       </c>
       <c r="T29" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>291.96</v>
+        <v>229.91</v>
       </c>
       <c r="D30" t="n">
-        <v>56.71</v>
+        <v>56.93</v>
       </c>
       <c r="E30" t="n">
-        <v>130.43</v>
+        <v>613.5700000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>4.85</v>
+        <v>22.29</v>
       </c>
       <c r="G30" t="n">
-        <v>15420090000</v>
+        <v>81837530000</v>
       </c>
       <c r="H30" t="n">
-        <v>233.57</v>
+        <v>183.93</v>
       </c>
       <c r="I30" t="n">
-        <v>351.75</v>
+        <v>241.25</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>20.48</v>
+        <v>4.93</v>
       </c>
       <c r="L30" t="n">
-        <v>47.47</v>
+        <v>32.15</v>
       </c>
       <c r="M30" t="n">
-        <v>47.51</v>
+        <v>115.46</v>
       </c>
       <c r="N30" t="n">
-        <v>23.19</v>
+        <v>79.86</v>
       </c>
       <c r="O30" t="n">
-        <v>3.82</v>
+        <v>3.69</v>
       </c>
       <c r="P30" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="R30" t="n">
-        <v>2.15</v>
+        <v>9.06</v>
       </c>
       <c r="S30" t="n">
-        <v>106.36</v>
+        <v>81.38</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="U30" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>130.66</v>
+        <v>414.73</v>
       </c>
       <c r="D31" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="E31" t="n">
-        <v>91.91</v>
+        <v>64.34</v>
       </c>
       <c r="F31" t="n">
-        <v>6.62</v>
+        <v>4.04</v>
       </c>
       <c r="G31" t="n">
-        <v>10702580000</v>
+        <v>18826680000</v>
       </c>
       <c r="H31" t="n">
-        <v>104.53</v>
+        <v>331.78</v>
       </c>
       <c r="I31" t="n">
-        <v>149.75</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
+        <v>478.62</v>
       </c>
       <c r="K31" t="n">
-        <v>14.61</v>
+        <v>15.41</v>
       </c>
       <c r="L31" t="n">
-        <v>54.3</v>
+        <v>21.64</v>
       </c>
       <c r="M31" t="n">
-        <v>36.23</v>
+        <v>145.11</v>
       </c>
       <c r="N31" t="n">
-        <v>24.54</v>
+        <v>63.43</v>
       </c>
       <c r="O31" t="n">
-        <v>7.3</v>
+        <v>-0.45</v>
       </c>
       <c r="P31" t="n">
-        <v>0.49</v>
+        <v>6.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="R31" t="n">
-        <v>16.68</v>
+        <v>1.84</v>
       </c>
       <c r="S31" t="n">
-        <v>88.28</v>
+        <v>103.78</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="U31" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>230</v>
+        <v>727.98</v>
       </c>
       <c r="D32" t="n">
-        <v>56.99</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>613.8200000000001</v>
+        <v>43.46</v>
       </c>
       <c r="F32" t="n">
-        <v>22.3</v>
+        <v>21.31</v>
       </c>
       <c r="G32" t="n">
-        <v>81870840000</v>
+        <v>250921690000</v>
       </c>
       <c r="H32" t="n">
-        <v>184</v>
+        <v>582.38</v>
       </c>
       <c r="I32" t="n">
-        <v>241.25</v>
+        <v>560</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>4.89</v>
+        <v>-23.07</v>
       </c>
       <c r="L32" t="n">
-        <v>32.15</v>
+        <v>45.47</v>
       </c>
       <c r="M32" t="n">
-        <v>115.46</v>
+        <v>483.37</v>
       </c>
       <c r="N32" t="n">
-        <v>79.86</v>
+        <v>45.39</v>
       </c>
       <c r="O32" t="n">
-        <v>3.69</v>
+        <v>54.28</v>
       </c>
       <c r="P32" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="R32" t="n">
-        <v>9.06</v>
+        <v>0.95</v>
       </c>
       <c r="S32" t="n">
-        <v>81.38</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="U32" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>840</v>
+        <v>279.22</v>
       </c>
       <c r="D33" t="n">
-        <v>49.85</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>28.11</v>
+        <v>93.16</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>37329830000</v>
+        <v>70265830000</v>
       </c>
       <c r="H33" t="n">
-        <v>672</v>
+        <v>223.38</v>
       </c>
       <c r="I33" t="n">
-        <v>1000.14</v>
+        <v>255.29</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>19.06</v>
+        <v>-8.57</v>
       </c>
       <c r="L33" t="n">
-        <v>19.67</v>
+        <v>621.52</v>
       </c>
       <c r="M33" t="n">
-        <v>30.04</v>
+        <v>521.4</v>
       </c>
       <c r="N33" t="n">
-        <v>19.29</v>
+        <v>7.48</v>
       </c>
       <c r="O33" t="n">
-        <v>7.54</v>
+        <v>95.27</v>
       </c>
       <c r="P33" t="n">
-        <v>0.13</v>
+        <v>1.31</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.13</v>
+        <v>4.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0.74</v>
+        <v>19.73</v>
       </c>
       <c r="S33" t="n">
-        <v>96.41</v>
+        <v>50.26</v>
       </c>
       <c r="T33" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>45.98</v>
+        <v>112.5</v>
       </c>
       <c r="D34" t="n">
-        <v>55.33</v>
+        <v>53.53</v>
       </c>
       <c r="E34" t="n">
-        <v>19.08</v>
+        <v>27.95</v>
       </c>
       <c r="F34" t="n">
-        <v>2.19</v>
+        <v>2.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2274200000</v>
+        <v>26740520000</v>
       </c>
       <c r="H34" t="n">
-        <v>36.78</v>
+        <v>90</v>
       </c>
       <c r="I34" t="n">
-        <v>59</v>
+        <v>152.31</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>28.32</v>
+        <v>35.39</v>
       </c>
       <c r="L34" t="n">
-        <v>11.04</v>
+        <v>2.71</v>
       </c>
       <c r="M34" t="n">
-        <v>-10.25</v>
+        <v>14.41</v>
       </c>
       <c r="N34" t="n">
-        <v>62.66</v>
+        <v>38.48</v>
       </c>
       <c r="O34" t="n">
-        <v>12.36</v>
+        <v>10.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0.66</v>
+        <v>0.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="R34" t="n">
-        <v>5.93</v>
+        <v>0.35</v>
       </c>
       <c r="S34" t="n">
-        <v>97.51000000000001</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="U34" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>112.65</v>
+        <v>135.8</v>
       </c>
       <c r="D35" t="n">
-        <v>53.93</v>
+        <v>56.12</v>
       </c>
       <c r="E35" t="n">
-        <v>27.99</v>
+        <v>95.53</v>
       </c>
       <c r="F35" t="n">
-        <v>2.95</v>
+        <v>6.88</v>
       </c>
       <c r="G35" t="n">
-        <v>26776170000</v>
+        <v>11123610000</v>
       </c>
       <c r="H35" t="n">
-        <v>90.12</v>
+        <v>108.64</v>
       </c>
       <c r="I35" t="n">
-        <v>152.31</v>
+        <v>149.75</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>35.21</v>
+        <v>10.27</v>
       </c>
       <c r="L35" t="n">
-        <v>2.71</v>
+        <v>54.3</v>
       </c>
       <c r="M35" t="n">
-        <v>14.41</v>
+        <v>36.23</v>
       </c>
       <c r="N35" t="n">
-        <v>38.48</v>
+        <v>24.54</v>
       </c>
       <c r="O35" t="n">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="P35" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="R35" t="n">
-        <v>0.35</v>
+        <v>16.68</v>
       </c>
       <c r="S35" t="n">
-        <v>95.73999999999999</v>
+        <v>88.28</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="U35" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="36">
@@ -2877,22 +2877,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26.32</v>
+        <v>26.25</v>
       </c>
       <c r="D36" t="n">
-        <v>55.45</v>
+        <v>54.61</v>
       </c>
       <c r="E36" t="n">
-        <v>19.97</v>
+        <v>19.92</v>
       </c>
       <c r="F36" t="n">
         <v>2.81</v>
       </c>
       <c r="G36" t="n">
-        <v>4118319999</v>
+        <v>4106590000</v>
       </c>
       <c r="H36" t="n">
-        <v>21.06</v>
+        <v>21</v>
       </c>
       <c r="I36" t="n">
         <v>32.2</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>22.34</v>
+        <v>22.67</v>
       </c>
       <c r="L36" t="n">
         <v>5.52</v>
@@ -2931,7 +2931,7 @@
         <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="37">
@@ -2942,125 +2942,125 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>127.79</v>
+        <v>189.44</v>
       </c>
       <c r="D37" t="n">
-        <v>54.85</v>
+        <v>51.83</v>
       </c>
       <c r="E37" t="n">
-        <v>140.32</v>
+        <v>50.11</v>
       </c>
       <c r="F37" t="n">
-        <v>5.25</v>
+        <v>10.37</v>
       </c>
       <c r="G37" t="n">
-        <v>38020680000</v>
+        <v>66569800000</v>
       </c>
       <c r="H37" t="n">
-        <v>102.23</v>
+        <v>151.55</v>
       </c>
       <c r="I37" t="n">
-        <v>131.55</v>
+        <v>219.17</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.94</v>
+        <v>15.69</v>
       </c>
       <c r="L37" t="n">
-        <v>21.58</v>
+        <v>16.16</v>
       </c>
       <c r="M37" t="n">
-        <v>787.08</v>
+        <v>67.62</v>
       </c>
       <c r="N37" t="n">
-        <v>40.39</v>
+        <v>25.66</v>
       </c>
       <c r="O37" t="n">
-        <v>3.76</v>
+        <v>20.83</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="S37" t="n">
-        <v>87.14</v>
+        <v>99.48</v>
       </c>
       <c r="T37" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U37" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>388.65</v>
+        <v>128.36</v>
       </c>
       <c r="D38" t="n">
-        <v>53.12</v>
+        <v>56.02</v>
       </c>
       <c r="E38" t="n">
-        <v>185.55</v>
+        <v>140.95</v>
       </c>
       <c r="F38" t="n">
-        <v>11.52</v>
+        <v>5.27</v>
       </c>
       <c r="G38" t="n">
-        <v>76035220000</v>
+        <v>38190090000</v>
       </c>
       <c r="H38" t="n">
-        <v>310.92</v>
+        <v>102.69</v>
       </c>
       <c r="I38" t="n">
-        <v>388.09</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
+        <v>131.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.14</v>
+        <v>2.49</v>
       </c>
       <c r="L38" t="n">
-        <v>20.55</v>
+        <v>21.58</v>
       </c>
       <c r="M38" t="n">
-        <v>990.95</v>
+        <v>787.08</v>
       </c>
       <c r="N38" t="n">
-        <v>37.93</v>
+        <v>40.39</v>
       </c>
       <c r="O38" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.32</v>
+        <v>3.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="R38" t="n">
-        <v>4.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>88.13</v>
+        <v>87.14</v>
       </c>
       <c r="T38" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="U38" t="n">
         <v>50</v>
@@ -3069,472 +3069,472 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>145.17</v>
+        <v>391.17</v>
       </c>
       <c r="D39" t="n">
-        <v>54.61</v>
+        <v>53.59</v>
       </c>
       <c r="E39" t="n">
-        <v>25.96</v>
+        <v>186.75</v>
       </c>
       <c r="F39" t="n">
-        <v>3.63</v>
+        <v>11.59</v>
       </c>
       <c r="G39" t="n">
-        <v>88570480000</v>
+        <v>76527260000</v>
       </c>
       <c r="H39" t="n">
-        <v>116.14</v>
+        <v>312.94</v>
       </c>
       <c r="I39" t="n">
-        <v>157.1</v>
+        <v>388.09</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>8.220000000000001</v>
+        <v>-0.79</v>
       </c>
       <c r="L39" t="n">
-        <v>8.210000000000001</v>
+        <v>20.55</v>
       </c>
       <c r="M39" t="n">
-        <v>38.05</v>
+        <v>990.95</v>
       </c>
       <c r="N39" t="n">
-        <v>36.49</v>
+        <v>37.93</v>
       </c>
       <c r="O39" t="n">
-        <v>14.45</v>
+        <v>6.07</v>
       </c>
       <c r="P39" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.32</v>
+        <v>2.04</v>
       </c>
       <c r="R39" t="n">
-        <v>0.34</v>
+        <v>4.45</v>
       </c>
       <c r="S39" t="n">
-        <v>92.81999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="T39" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="U39" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>191.2</v>
+        <v>681.33</v>
       </c>
       <c r="D40" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="E40" t="n">
-        <v>50.57</v>
+        <v>57.56</v>
       </c>
       <c r="F40" t="n">
-        <v>10.47</v>
+        <v>34.05</v>
       </c>
       <c r="G40" t="n">
-        <v>67188830000</v>
+        <v>173442170000</v>
       </c>
       <c r="H40" t="n">
-        <v>152.96</v>
+        <v>545.0599999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>219.17</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
+        <v>720.9299999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>14.63</v>
+        <v>5.81</v>
       </c>
       <c r="L40" t="n">
-        <v>16.16</v>
+        <v>25.57</v>
       </c>
       <c r="M40" t="n">
-        <v>67.62</v>
+        <v>124.28</v>
       </c>
       <c r="N40" t="n">
-        <v>25.66</v>
+        <v>74.89</v>
       </c>
       <c r="O40" t="n">
-        <v>20.83</v>
+        <v>-0.89</v>
       </c>
       <c r="P40" t="n">
-        <v>0.82</v>
+        <v>0.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="R40" t="n">
-        <v>0.03</v>
+        <v>3.52</v>
       </c>
       <c r="S40" t="n">
-        <v>99.48</v>
+        <v>71.22</v>
       </c>
       <c r="T40" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U40" t="n">
-        <v>49.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>675.96</v>
+        <v>287.92</v>
       </c>
       <c r="D41" t="n">
-        <v>56.47</v>
+        <v>55.88</v>
       </c>
       <c r="F41" t="n">
-        <v>33.78</v>
+        <v>33.44</v>
       </c>
       <c r="G41" t="n">
-        <v>172076840000</v>
+        <v>81896380000</v>
       </c>
       <c r="H41" t="n">
-        <v>540.77</v>
+        <v>230.34</v>
       </c>
       <c r="I41" t="n">
-        <v>720.9299999999999</v>
+        <v>279.01</v>
       </c>
       <c r="K41" t="n">
-        <v>6.65</v>
+        <v>-3.09</v>
       </c>
       <c r="L41" t="n">
-        <v>25.57</v>
+        <v>130.37</v>
       </c>
       <c r="M41" t="n">
-        <v>124.28</v>
+        <v>313.73</v>
       </c>
       <c r="N41" t="n">
-        <v>74.89</v>
+        <v>31.08</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.89</v>
+        <v>0.25</v>
       </c>
       <c r="P41" t="n">
-        <v>0.18</v>
+        <v>3.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.26</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>3.52</v>
+        <v>6.31</v>
       </c>
       <c r="S41" t="n">
-        <v>71.22</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="T41" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="U41" t="n">
-        <v>49.7</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>285.25</v>
+        <v>523.5</v>
       </c>
       <c r="D42" t="n">
-        <v>55.19</v>
+        <v>59.2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>171.81</v>
       </c>
       <c r="F42" t="n">
-        <v>33.13</v>
+        <v>22.79</v>
       </c>
       <c r="G42" t="n">
-        <v>81137620000</v>
+        <v>853619410000</v>
       </c>
       <c r="H42" t="n">
-        <v>228.2</v>
+        <v>418.8</v>
       </c>
       <c r="I42" t="n">
-        <v>279.01</v>
+        <v>496.32</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.19</v>
+        <v>-5.19</v>
       </c>
       <c r="L42" t="n">
-        <v>130.37</v>
+        <v>37.85</v>
       </c>
       <c r="M42" t="n">
-        <v>313.73</v>
+        <v>92.25</v>
       </c>
       <c r="N42" t="n">
-        <v>31.08</v>
+        <v>47.09</v>
       </c>
       <c r="O42" t="n">
-        <v>0.25</v>
+        <v>13.37</v>
       </c>
       <c r="P42" t="n">
-        <v>3.2</v>
+        <v>0.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="R42" t="n">
-        <v>6.31</v>
+        <v>0.49</v>
       </c>
       <c r="S42" t="n">
-        <v>85.98999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="U42" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>521</v>
+        <v>115.31</v>
       </c>
       <c r="D43" t="n">
-        <v>58.87</v>
+        <v>58.28</v>
       </c>
       <c r="E43" t="n">
-        <v>170.99</v>
+        <v>83.75</v>
       </c>
       <c r="F43" t="n">
-        <v>22.68</v>
+        <v>6.69</v>
       </c>
       <c r="G43" t="n">
-        <v>849542910000</v>
+        <v>20040860000</v>
       </c>
       <c r="H43" t="n">
-        <v>416.8</v>
+        <v>92.25</v>
       </c>
       <c r="I43" t="n">
-        <v>496.32</v>
+        <v>120.2</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.74</v>
+        <v>4.24</v>
       </c>
       <c r="L43" t="n">
-        <v>37.85</v>
+        <v>11.19</v>
       </c>
       <c r="M43" t="n">
-        <v>92.25</v>
+        <v>20.1</v>
       </c>
       <c r="N43" t="n">
-        <v>47.09</v>
+        <v>77.44</v>
       </c>
       <c r="O43" t="n">
-        <v>13.37</v>
+        <v>8.24</v>
       </c>
       <c r="P43" t="n">
         <v>0.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.49</v>
+        <v>0.8</v>
       </c>
       <c r="R43" t="n">
-        <v>0.49</v>
+        <v>4.97</v>
       </c>
       <c r="S43" t="n">
-        <v>68.29000000000001</v>
+        <v>93.41</v>
       </c>
       <c r="T43" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="U43" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>159.21</v>
+        <v>148.34</v>
       </c>
       <c r="D44" t="n">
-        <v>57.1</v>
+        <v>58.49</v>
       </c>
       <c r="E44" t="n">
-        <v>26.59</v>
+        <v>26.53</v>
       </c>
       <c r="F44" t="n">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="G44" t="n">
-        <v>53682820000</v>
+        <v>90501500000</v>
       </c>
       <c r="H44" t="n">
-        <v>127.37</v>
+        <v>118.67</v>
       </c>
       <c r="I44" t="n">
-        <v>230.29</v>
+        <v>157.1</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>44.65</v>
+        <v>5.91</v>
       </c>
       <c r="L44" t="n">
-        <v>-10</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>407.29</v>
+        <v>38.05</v>
       </c>
       <c r="N44" t="n">
-        <v>14.65</v>
+        <v>36.49</v>
       </c>
       <c r="O44" t="n">
-        <v>12.45</v>
+        <v>14.45</v>
       </c>
       <c r="P44" t="n">
-        <v>3.56</v>
+        <v>0.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="R44" t="n">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="S44" t="n">
-        <v>90.03</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="U44" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>115.75</v>
+        <v>160.81</v>
       </c>
       <c r="D45" t="n">
-        <v>58.77</v>
+        <v>58.36</v>
       </c>
       <c r="E45" t="n">
-        <v>84.06999999999999</v>
+        <v>26.85</v>
       </c>
       <c r="F45" t="n">
-        <v>6.72</v>
+        <v>3.3</v>
       </c>
       <c r="G45" t="n">
-        <v>20118200000</v>
+        <v>54222310000</v>
       </c>
       <c r="H45" t="n">
-        <v>92.59999999999999</v>
+        <v>128.65</v>
       </c>
       <c r="I45" t="n">
-        <v>120.2</v>
+        <v>230.29</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>3.84</v>
+        <v>43.21</v>
       </c>
       <c r="L45" t="n">
-        <v>11.19</v>
+        <v>-10</v>
       </c>
       <c r="M45" t="n">
-        <v>20.1</v>
+        <v>407.29</v>
       </c>
       <c r="N45" t="n">
-        <v>77.44</v>
+        <v>14.65</v>
       </c>
       <c r="O45" t="n">
-        <v>8.24</v>
+        <v>12.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0.06</v>
+        <v>3.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="R45" t="n">
-        <v>4.97</v>
+        <v>0.97</v>
       </c>
       <c r="S45" t="n">
-        <v>93.41</v>
+        <v>90.03</v>
       </c>
       <c r="T45" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="U45" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="46">
@@ -3549,22 +3549,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>35.42</v>
+        <v>35.94</v>
       </c>
       <c r="D46" t="n">
-        <v>59.86</v>
+        <v>61.85</v>
       </c>
       <c r="E46" t="n">
-        <v>48.13</v>
+        <v>48.84</v>
       </c>
       <c r="F46" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="G46" t="n">
-        <v>9338820000</v>
+        <v>9475920000</v>
       </c>
       <c r="H46" t="n">
-        <v>28.34</v>
+        <v>28.75</v>
       </c>
       <c r="I46" t="n">
         <v>41.56</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>17.33</v>
+        <v>15.64</v>
       </c>
       <c r="L46" t="n">
         <v>14.57</v>
@@ -3600,7 +3600,7 @@
         <v>2.29</v>
       </c>
       <c r="U46" t="n">
-        <v>48.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="47">
@@ -3615,22 +3615,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>402.81</v>
+        <v>403.42</v>
       </c>
       <c r="D47" t="n">
-        <v>42.6</v>
+        <v>43.02</v>
       </c>
       <c r="E47" t="n">
-        <v>32.47</v>
+        <v>32.52</v>
       </c>
       <c r="F47" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="G47" t="n">
-        <v>66864460000</v>
+        <v>66965940000</v>
       </c>
       <c r="H47" t="n">
-        <v>322.25</v>
+        <v>322.74</v>
       </c>
       <c r="I47" t="n">
         <v>509.2</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>26.41</v>
+        <v>26.22</v>
       </c>
       <c r="L47" t="n">
         <v>7.36</v>
@@ -3669,7 +3669,7 @@
         <v>1.47</v>
       </c>
       <c r="U47" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="48">
@@ -3680,131 +3680,131 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>170</v>
+        <v>717.0700000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>56.79</v>
+        <v>53.21</v>
       </c>
       <c r="E48" t="n">
-        <v>57.17</v>
+        <v>98.38</v>
       </c>
       <c r="F48" t="n">
-        <v>6.36</v>
+        <v>3.57</v>
       </c>
       <c r="G48" t="n">
-        <v>27492480000</v>
+        <v>107603630000</v>
       </c>
       <c r="H48" t="n">
-        <v>136</v>
+        <v>573.66</v>
       </c>
       <c r="I48" t="n">
-        <v>194.67</v>
+        <v>802.79</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>14.51</v>
+        <v>11.95</v>
       </c>
       <c r="L48" t="n">
-        <v>53.47</v>
+        <v>26.33</v>
       </c>
       <c r="M48" t="n">
-        <v>-60.21</v>
+        <v>51.81</v>
       </c>
       <c r="N48" t="n">
-        <v>37.01</v>
+        <v>13.3</v>
       </c>
       <c r="O48" t="n">
-        <v>11.26</v>
+        <v>3.67</v>
       </c>
       <c r="P48" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="R48" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S48" t="n">
-        <v>93.70999999999999</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="T48" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="U48" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>41.46</v>
+        <v>171.17</v>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>57.82</v>
       </c>
       <c r="E49" t="n">
-        <v>77.34</v>
+        <v>57.56</v>
       </c>
       <c r="F49" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="G49" t="n">
-        <v>12084580000</v>
+        <v>27681460000</v>
       </c>
       <c r="H49" t="n">
-        <v>33.17</v>
+        <v>136.94</v>
       </c>
       <c r="I49" t="n">
-        <v>45.25</v>
+        <v>194.67</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>9.140000000000001</v>
+        <v>13.73</v>
       </c>
       <c r="L49" t="n">
-        <v>19.44</v>
+        <v>53.47</v>
       </c>
       <c r="M49" t="n">
-        <v>-54.84</v>
+        <v>-60.21</v>
       </c>
       <c r="N49" t="n">
-        <v>81.56</v>
+        <v>37.01</v>
       </c>
       <c r="O49" t="n">
-        <v>8.06</v>
+        <v>11.26</v>
       </c>
       <c r="P49" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.74</v>
+        <v>1.36</v>
       </c>
       <c r="R49" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="S49" t="n">
-        <v>101.95</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="T49" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="U49" t="n">
         <v>47.2</v>
@@ -3813,70 +3813,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>727.84</v>
+        <v>41.78</v>
       </c>
       <c r="D50" t="n">
-        <v>55.63</v>
+        <v>55.32</v>
       </c>
       <c r="E50" t="n">
-        <v>99.84999999999999</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>3.63</v>
+        <v>6.03</v>
       </c>
       <c r="G50" t="n">
-        <v>109219180000</v>
+        <v>12177850000</v>
       </c>
       <c r="H50" t="n">
-        <v>582.27</v>
+        <v>33.42</v>
       </c>
       <c r="I50" t="n">
-        <v>802.79</v>
+        <v>45.25</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>10.3</v>
+        <v>8.31</v>
       </c>
       <c r="L50" t="n">
-        <v>26.33</v>
+        <v>19.44</v>
       </c>
       <c r="M50" t="n">
-        <v>51.81</v>
+        <v>-54.84</v>
       </c>
       <c r="N50" t="n">
-        <v>13.3</v>
+        <v>81.56</v>
       </c>
       <c r="O50" t="n">
-        <v>3.67</v>
+        <v>8.06</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7</v>
+        <v>0.06</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="R50" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.23999999999999</v>
+        <v>101.95</v>
       </c>
       <c r="T50" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="U50" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="51">
@@ -3891,22 +3891,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>412.3</v>
+        <v>414.93</v>
       </c>
       <c r="D51" t="n">
-        <v>54.89</v>
+        <v>55.85</v>
       </c>
       <c r="E51" t="n">
-        <v>40.31</v>
+        <v>40.56</v>
       </c>
       <c r="F51" t="n">
-        <v>5.61</v>
+        <v>5.65</v>
       </c>
       <c r="G51" t="n">
-        <v>160096080000</v>
+        <v>161117310000</v>
       </c>
       <c r="H51" t="n">
-        <v>329.84</v>
+        <v>331.94</v>
       </c>
       <c r="I51" t="n">
         <v>463.71</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>12.47</v>
+        <v>11.76</v>
       </c>
       <c r="L51" t="n">
         <v>16.84</v>
@@ -3945,7 +3945,7 @@
         <v>1.7</v>
       </c>
       <c r="U51" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>269.4</v>
+        <v>272.89</v>
       </c>
       <c r="D52" t="n">
-        <v>55.36</v>
+        <v>56.29</v>
       </c>
       <c r="E52" t="n">
-        <v>125.13</v>
+        <v>126.75</v>
       </c>
       <c r="F52" t="n">
-        <v>18.57</v>
+        <v>18.81</v>
       </c>
       <c r="G52" t="n">
-        <v>30107240000</v>
+        <v>30497270000</v>
       </c>
       <c r="H52" t="n">
-        <v>215.52</v>
+        <v>218.31</v>
       </c>
       <c r="I52" t="n">
         <v>313.83</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>16.49</v>
+        <v>15</v>
       </c>
       <c r="L52" t="n">
         <v>15.48</v>
@@ -4014,7 +4014,7 @@
         <v>1.5</v>
       </c>
       <c r="U52" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="53">
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>382.6</v>
+        <v>388.68</v>
       </c>
       <c r="D53" t="n">
-        <v>67.23999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="E53" t="n">
-        <v>72.20999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="F53" t="n">
-        <v>22.07</v>
+        <v>22.42</v>
       </c>
       <c r="G53" t="n">
-        <v>478468490000</v>
+        <v>486071950000</v>
       </c>
       <c r="H53" t="n">
-        <v>306.08</v>
+        <v>310.94</v>
       </c>
       <c r="I53" t="n">
         <v>337.34</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-11.83</v>
+        <v>-13.21</v>
       </c>
       <c r="L53" t="n">
         <v>23.76</v>
@@ -4083,7 +4083,7 @@
         <v>1.57</v>
       </c>
       <c r="U53" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="54">
@@ -4098,25 +4098,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>117.32</v>
+        <v>118.93</v>
       </c>
       <c r="D54" t="n">
-        <v>58.03</v>
+        <v>59.04</v>
       </c>
       <c r="F54" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="G54" t="n">
-        <v>64006320000</v>
+        <v>64881960000</v>
       </c>
       <c r="H54" t="n">
-        <v>93.86</v>
+        <v>95.14</v>
       </c>
       <c r="I54" t="n">
         <v>138.91</v>
       </c>
       <c r="K54" t="n">
-        <v>18.4</v>
+        <v>16.8</v>
       </c>
       <c r="L54" t="n">
         <v>111.69</v>
@@ -4146,73 +4146,67 @@
         <v>1.92</v>
       </c>
       <c r="U54" t="n">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>591</v>
+        <v>45.95</v>
       </c>
       <c r="D55" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="E55" t="n">
-        <v>55.53</v>
+        <v>56.32</v>
       </c>
       <c r="F55" t="n">
-        <v>16.17</v>
+        <v>36.94</v>
       </c>
       <c r="G55" t="n">
-        <v>469230010000</v>
+        <v>13131110000</v>
       </c>
       <c r="H55" t="n">
-        <v>472.8</v>
+        <v>36.76</v>
       </c>
       <c r="I55" t="n">
-        <v>529.8200000000001</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
+        <v>72.92</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.35</v>
+        <v>58.69</v>
       </c>
       <c r="L55" t="n">
-        <v>11.41</v>
+        <v>139.29</v>
       </c>
       <c r="M55" t="n">
-        <v>33.44</v>
+        <v>-120.39</v>
       </c>
       <c r="N55" t="n">
-        <v>48.96</v>
+        <v>27.07</v>
       </c>
       <c r="O55" t="n">
-        <v>29.31</v>
+        <v>-54.12</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.63</v>
+        <v>5.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0.46</v>
+        <v>9.48</v>
       </c>
       <c r="S55" t="n">
-        <v>81.87</v>
+        <v>70.27</v>
       </c>
       <c r="T55" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U55" t="n">
         <v>43.6</v>
@@ -4230,22 +4224,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1054.9</v>
+        <v>1081.11</v>
       </c>
       <c r="D56" t="n">
-        <v>73.15000000000001</v>
+        <v>74.63</v>
       </c>
       <c r="E56" t="n">
-        <v>100.13</v>
+        <v>102.62</v>
       </c>
       <c r="F56" t="n">
-        <v>21.48</v>
+        <v>22.02</v>
       </c>
       <c r="G56" t="n">
-        <v>236539170000</v>
+        <v>242416200000</v>
       </c>
       <c r="H56" t="n">
-        <v>843.92</v>
+        <v>864.89</v>
       </c>
       <c r="I56" t="n">
         <v>903.55</v>
@@ -4254,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>-14.35</v>
+        <v>-16.42</v>
       </c>
       <c r="L56" t="n">
         <v>44.07</v>
@@ -4284,139 +4278,145 @@
         <v>1.59</v>
       </c>
       <c r="U56" t="n">
-        <v>43.3</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>46.9</v>
+        <v>299.18</v>
       </c>
       <c r="D57" t="n">
-        <v>57.96</v>
+        <v>55.59</v>
+      </c>
+      <c r="E57" t="n">
+        <v>58.47</v>
       </c>
       <c r="F57" t="n">
-        <v>37.71</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>13402340000</v>
+        <v>10899690000</v>
       </c>
       <c r="H57" t="n">
-        <v>37.52</v>
+        <v>239.34</v>
       </c>
       <c r="I57" t="n">
-        <v>72.92</v>
+        <v>289.17</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>55.48</v>
+        <v>-3.35</v>
       </c>
       <c r="L57" t="n">
-        <v>139.29</v>
+        <v>6.45</v>
       </c>
       <c r="M57" t="n">
-        <v>-120.39</v>
+        <v>-1.12</v>
       </c>
       <c r="N57" t="n">
-        <v>27.07</v>
+        <v>30.05</v>
       </c>
       <c r="O57" t="n">
-        <v>-54.12</v>
+        <v>16.51</v>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.65</v>
+        <v>1.13</v>
       </c>
       <c r="R57" t="n">
-        <v>9.48</v>
+        <v>21.68</v>
       </c>
       <c r="S57" t="n">
-        <v>70.27</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="U57" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>POWL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>296.28</v>
+        <v>611.5</v>
       </c>
       <c r="D58" t="n">
-        <v>54.61</v>
+        <v>75.31</v>
       </c>
       <c r="E58" t="n">
-        <v>57.9</v>
+        <v>57.46</v>
       </c>
       <c r="F58" t="n">
-        <v>9.529999999999999</v>
+        <v>16.73</v>
       </c>
       <c r="G58" t="n">
-        <v>10793960000</v>
+        <v>485506180000</v>
       </c>
       <c r="H58" t="n">
-        <v>237.02</v>
+        <v>489.2</v>
       </c>
       <c r="I58" t="n">
-        <v>289.17</v>
+        <v>529.8200000000001</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.4</v>
+        <v>-13.36</v>
       </c>
       <c r="L58" t="n">
-        <v>6.45</v>
+        <v>11.41</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.12</v>
+        <v>33.44</v>
       </c>
       <c r="N58" t="n">
-        <v>30.05</v>
+        <v>48.96</v>
       </c>
       <c r="O58" t="n">
-        <v>16.51</v>
+        <v>29.31</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="R58" t="n">
-        <v>21.68</v>
+        <v>0.46</v>
       </c>
       <c r="S58" t="n">
-        <v>81.45999999999999</v>
+        <v>81.87</v>
       </c>
       <c r="T58" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="U58" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="59">
@@ -4431,22 +4431,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>135.14</v>
+        <v>136</v>
       </c>
       <c r="D59" t="n">
-        <v>62.7</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>30.56</v>
+        <v>30.76</v>
       </c>
       <c r="F59" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="G59" t="n">
-        <v>3944140000</v>
+        <v>3969350000</v>
       </c>
       <c r="H59" t="n">
-        <v>108.11</v>
+        <v>108.8</v>
       </c>
       <c r="I59" t="n">
         <v>147</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>8.779999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="L59" t="n">
         <v>-8.970000000000001</v>
@@ -4485,136 +4485,142 @@
         <v>2.13</v>
       </c>
       <c r="U59" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>278.6</v>
+        <v>1088.51</v>
       </c>
       <c r="D60" t="n">
-        <v>62.5</v>
+        <v>57.23</v>
       </c>
       <c r="E60" t="n">
-        <v>229.17</v>
+        <v>75.28</v>
       </c>
       <c r="F60" t="n">
-        <v>21.41</v>
+        <v>11.38</v>
       </c>
       <c r="G60" t="n">
-        <v>227059010000</v>
+        <v>107353480000</v>
       </c>
       <c r="H60" t="n">
-        <v>222.88</v>
+        <v>870.8099999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>320.25</v>
+        <v>1204.61</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>14.95</v>
+        <v>10.67</v>
       </c>
       <c r="L60" t="n">
-        <v>31.15</v>
+        <v>9.84</v>
       </c>
       <c r="M60" t="n">
-        <v>-159.65</v>
+        <v>19.96</v>
       </c>
       <c r="N60" t="n">
-        <v>71.94</v>
+        <v>27.71</v>
       </c>
       <c r="O60" t="n">
-        <v>7.95</v>
+        <v>15.07</v>
       </c>
       <c r="P60" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="R60" t="n">
-        <v>1.02</v>
+        <v>0.32</v>
       </c>
       <c r="S60" t="n">
-        <v>79.20999999999999</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="U60" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HYLN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.44</v>
+        <v>279.4</v>
       </c>
       <c r="D61" t="n">
-        <v>65.45</v>
+        <v>63.05</v>
+      </c>
+      <c r="E61" t="n">
+        <v>229.83</v>
       </c>
       <c r="F61" t="n">
-        <v>227.96</v>
+        <v>21.47</v>
       </c>
       <c r="G61" t="n">
-        <v>1326750000</v>
+        <v>227715000000</v>
       </c>
       <c r="H61" t="n">
-        <v>5.95</v>
+        <v>223.52</v>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>320.25</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.91</v>
+        <v>14.62</v>
       </c>
       <c r="L61" t="n">
-        <v>479.14</v>
+        <v>31.15</v>
       </c>
       <c r="M61" t="n">
-        <v>33.23</v>
+        <v>-159.65</v>
       </c>
       <c r="N61" t="n">
-        <v>-112.67</v>
+        <v>71.94</v>
       </c>
       <c r="O61" t="n">
-        <v>-888.12</v>
+        <v>7.95</v>
       </c>
       <c r="P61" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.42</v>
+        <v>0.95</v>
       </c>
       <c r="R61" t="n">
-        <v>32.13</v>
+        <v>1.02</v>
       </c>
       <c r="S61" t="n">
-        <v>24.99</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="T61" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U61" t="n">
         <v>41.5</v>
@@ -4623,70 +4629,64 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>HYLN</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1096.5</v>
+        <v>7.66</v>
       </c>
       <c r="D62" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>75.83</v>
+        <v>66.91</v>
       </c>
       <c r="F62" t="n">
-        <v>11.46</v>
+        <v>234.86</v>
       </c>
       <c r="G62" t="n">
-        <v>108141490000</v>
+        <v>1366880000</v>
       </c>
       <c r="H62" t="n">
-        <v>877.2</v>
+        <v>6.13</v>
       </c>
       <c r="I62" t="n">
-        <v>1204.61</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>9.859999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>9.84</v>
+        <v>479.14</v>
       </c>
       <c r="M62" t="n">
-        <v>19.96</v>
+        <v>33.23</v>
       </c>
       <c r="N62" t="n">
-        <v>27.71</v>
+        <v>-112.67</v>
       </c>
       <c r="O62" t="n">
-        <v>15.07</v>
+        <v>-888.12</v>
       </c>
       <c r="P62" t="n">
-        <v>1.63</v>
+        <v>0.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.96</v>
+        <v>3.42</v>
       </c>
       <c r="R62" t="n">
-        <v>0.32</v>
+        <v>32.13</v>
       </c>
       <c r="S62" t="n">
-        <v>99.01000000000001</v>
+        <v>24.99</v>
       </c>
       <c r="T62" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="U62" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -4701,25 +4701,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23.91</v>
+        <v>23.97</v>
       </c>
       <c r="D63" t="n">
-        <v>54.9</v>
+        <v>55.03</v>
       </c>
       <c r="F63" t="n">
         <v>1.71</v>
       </c>
       <c r="G63" t="n">
-        <v>4407730000</v>
+        <v>4417930000</v>
       </c>
       <c r="H63" t="n">
-        <v>19.13</v>
+        <v>19.18</v>
       </c>
       <c r="I63" t="n">
         <v>18.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-22</v>
+        <v>-22.19</v>
       </c>
       <c r="L63" t="n">
         <v>7.71</v>
@@ -4764,31 +4764,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>245.98</v>
+        <v>245.33</v>
       </c>
       <c r="D64" t="n">
-        <v>66.36</v>
+        <v>66.17</v>
       </c>
       <c r="E64" t="n">
-        <v>69.54000000000001</v>
+        <v>69.36</v>
       </c>
       <c r="F64" t="n">
-        <v>24.55</v>
+        <v>24.48</v>
       </c>
       <c r="G64" t="n">
-        <v>321317580000</v>
+        <v>320468510000</v>
       </c>
       <c r="H64" t="n">
-        <v>196.78</v>
+        <v>196.26</v>
       </c>
       <c r="I64" t="n">
-        <v>197.06</v>
+        <v>200</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>-19.89</v>
+        <v>-18.48</v>
       </c>
       <c r="L64" t="n">
         <v>11.52</v>
@@ -4818,7 +4818,7 @@
         <v>2.03</v>
       </c>
       <c r="U64" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -4833,31 +4833,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>326.9</v>
+        <v>329.95</v>
       </c>
       <c r="D65" t="n">
-        <v>63.89</v>
+        <v>64.55</v>
       </c>
       <c r="E65" t="n">
-        <v>151.76</v>
+        <v>153.17</v>
       </c>
       <c r="F65" t="n">
-        <v>15.78</v>
+        <v>15.93</v>
       </c>
       <c r="G65" t="n">
-        <v>16261170000</v>
+        <v>16412640000</v>
       </c>
       <c r="H65" t="n">
-        <v>261.52</v>
+        <v>263.96</v>
       </c>
       <c r="I65" t="n">
-        <v>351.6</v>
+        <v>353.27</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>7.56</v>
+        <v>7.07</v>
       </c>
       <c r="L65" t="n">
         <v>9.51</v>
@@ -4884,10 +4884,10 @@
         <v>99.22</v>
       </c>
       <c r="T65" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="U65" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="66">
@@ -4898,134 +4898,134 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>81.40000000000001</v>
+        <v>180.94</v>
       </c>
       <c r="D66" t="n">
-        <v>56.07</v>
+        <v>61.04</v>
       </c>
       <c r="E66" t="n">
-        <v>58.48</v>
+        <v>56.37</v>
       </c>
       <c r="F66" t="n">
-        <v>6.53</v>
+        <v>6.58</v>
       </c>
       <c r="G66" t="n">
-        <v>44641100000</v>
+        <v>5560920000</v>
       </c>
       <c r="H66" t="n">
-        <v>65.12</v>
+        <v>144.75</v>
       </c>
       <c r="I66" t="n">
-        <v>80.7</v>
+        <v>161</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.86</v>
+        <v>-11.02</v>
       </c>
       <c r="L66" t="n">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="M66" t="n">
-        <v>-51.3</v>
+        <v>-66.34999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>26.11</v>
+        <v>43.07</v>
       </c>
       <c r="O66" t="n">
-        <v>11.37</v>
+        <v>11.93</v>
       </c>
       <c r="P66" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="R66" t="n">
-        <v>76.16</v>
+        <v>1.43</v>
       </c>
       <c r="S66" t="n">
-        <v>25.64</v>
+        <v>111.62</v>
       </c>
       <c r="T66" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="U66" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>229.66</v>
+        <v>82.37</v>
       </c>
       <c r="D67" t="n">
-        <v>56.89</v>
+        <v>57.12</v>
       </c>
       <c r="E67" t="n">
-        <v>32.55</v>
+        <v>59.17</v>
       </c>
       <c r="F67" t="n">
-        <v>3.67</v>
+        <v>6.6</v>
       </c>
       <c r="G67" t="n">
-        <v>145524780000</v>
+        <v>45173060000</v>
       </c>
       <c r="H67" t="n">
-        <v>183.73</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>251.87</v>
+        <v>80.7</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>9.67</v>
+        <v>-2.03</v>
       </c>
       <c r="L67" t="n">
-        <v>-6.9</v>
+        <v>3.09</v>
       </c>
       <c r="M67" t="n">
-        <v>-42.16</v>
+        <v>-51.3</v>
       </c>
       <c r="N67" t="n">
-        <v>38.06</v>
+        <v>26.11</v>
       </c>
       <c r="O67" t="n">
         <v>11.37</v>
       </c>
       <c r="P67" t="n">
-        <v>2.78</v>
+        <v>0.15</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.85</v>
+        <v>1.77</v>
       </c>
       <c r="R67" t="n">
-        <v>0.1</v>
+        <v>76.16</v>
       </c>
       <c r="S67" t="n">
-        <v>78.48</v>
+        <v>25.64</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U67" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="68">
@@ -5040,22 +5040,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>71.23</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>63.21</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>46.8</v>
+        <v>47.13</v>
       </c>
       <c r="F68" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="G68" t="n">
-        <v>59162250000</v>
+        <v>59581690000</v>
       </c>
       <c r="H68" t="n">
-        <v>56.98</v>
+        <v>57.39</v>
       </c>
       <c r="I68" t="n">
         <v>76.40000000000001</v>
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>7.26</v>
+        <v>6.5</v>
       </c>
       <c r="L68" t="n">
         <v>2.36</v>
@@ -5094,145 +5094,145 @@
         <v>2.03</v>
       </c>
       <c r="U68" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>286.92</v>
+        <v>232.87</v>
       </c>
       <c r="D69" t="n">
-        <v>60.73</v>
+        <v>59.22</v>
       </c>
       <c r="E69" t="n">
-        <v>98.05</v>
+        <v>33.01</v>
       </c>
       <c r="F69" t="n">
-        <v>28.79</v>
+        <v>3.72</v>
       </c>
       <c r="G69" t="n">
-        <v>250999010000</v>
+        <v>147555640000</v>
       </c>
       <c r="H69" t="n">
-        <v>229.54</v>
+        <v>186.3</v>
       </c>
       <c r="I69" t="n">
-        <v>244.35</v>
+        <v>251.87</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>-14.84</v>
+        <v>8.16</v>
       </c>
       <c r="L69" t="n">
-        <v>27.57</v>
+        <v>-6.9</v>
       </c>
       <c r="M69" t="n">
-        <v>-81</v>
+        <v>-42.16</v>
       </c>
       <c r="N69" t="n">
-        <v>50.64</v>
+        <v>38.06</v>
       </c>
       <c r="O69" t="n">
-        <v>28.99</v>
+        <v>11.37</v>
       </c>
       <c r="P69" t="n">
-        <v>0.3</v>
+        <v>2.78</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.22</v>
+        <v>0.85</v>
       </c>
       <c r="R69" t="n">
-        <v>0.77</v>
+        <v>0.1</v>
       </c>
       <c r="S69" t="n">
-        <v>78.14</v>
+        <v>78.48</v>
       </c>
       <c r="T69" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>182</v>
+        <v>293.06</v>
       </c>
       <c r="D70" t="n">
-        <v>61.45</v>
+        <v>61.73</v>
       </c>
       <c r="E70" t="n">
-        <v>56.7</v>
+        <v>100.14</v>
       </c>
       <c r="F70" t="n">
-        <v>6.62</v>
+        <v>29.41</v>
       </c>
       <c r="G70" t="n">
-        <v>5593570000</v>
+        <v>256368880000</v>
       </c>
       <c r="H70" t="n">
-        <v>145.6</v>
+        <v>234.45</v>
       </c>
       <c r="I70" t="n">
-        <v>161</v>
+        <v>244.35</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-11.54</v>
+        <v>-16.62</v>
       </c>
       <c r="L70" t="n">
-        <v>3.32</v>
+        <v>27.57</v>
       </c>
       <c r="M70" t="n">
-        <v>-66.34999999999999</v>
+        <v>-81</v>
       </c>
       <c r="N70" t="n">
-        <v>43.07</v>
+        <v>50.64</v>
       </c>
       <c r="O70" t="n">
-        <v>11.93</v>
+        <v>28.99</v>
       </c>
       <c r="P70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="R70" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S70" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="T70" t="n">
         <v>1.43</v>
       </c>
-      <c r="S70" t="n">
-        <v>111.62</v>
-      </c>
-      <c r="T70" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U70" t="n">
-        <v>37.7</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="71">
@@ -5247,25 +5247,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>121.43</v>
+        <v>121.64</v>
       </c>
       <c r="D71" t="n">
-        <v>57.54</v>
+        <v>57.66</v>
       </c>
       <c r="F71" t="n">
-        <v>11.35</v>
+        <v>11.37</v>
       </c>
       <c r="G71" t="n">
-        <v>610307190000</v>
+        <v>611337530000</v>
       </c>
       <c r="H71" t="n">
-        <v>97.14</v>
+        <v>97.31</v>
       </c>
       <c r="I71" t="n">
         <v>100.81</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.98</v>
+        <v>-17.12</v>
       </c>
       <c r="L71" t="n">
         <v>7.18</v>
@@ -5301,127 +5301,127 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9.970000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="D72" t="n">
-        <v>42.8</v>
+        <v>55.1</v>
       </c>
       <c r="F72" t="n">
-        <v>195.13</v>
+        <v>6.18</v>
       </c>
       <c r="G72" t="n">
-        <v>3643120000</v>
+        <v>1547350000</v>
       </c>
       <c r="H72" t="n">
-        <v>7.98</v>
+        <v>8.52</v>
       </c>
       <c r="I72" t="n">
-        <v>15.64</v>
+        <v>8.82</v>
       </c>
       <c r="K72" t="n">
-        <v>56.87</v>
+        <v>-17.18</v>
       </c>
       <c r="L72" t="n">
-        <v>-95.78</v>
+        <v>-52.54</v>
       </c>
       <c r="M72" t="n">
-        <v>-25.52</v>
+        <v>-32.13</v>
       </c>
       <c r="N72" t="n">
-        <v>19.69</v>
+        <v>35</v>
       </c>
       <c r="O72" t="n">
-        <v>-2066.55</v>
+        <v>-187.95</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="R72" t="n">
-        <v>3.08</v>
+        <v>12.61</v>
       </c>
       <c r="S72" t="n">
-        <v>48.92</v>
+        <v>59.16</v>
       </c>
       <c r="T72" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="U72" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.9</v>
+        <v>10.39</v>
       </c>
       <c r="D73" t="n">
-        <v>58.95</v>
+        <v>45.61</v>
       </c>
       <c r="F73" t="n">
-        <v>6.33</v>
+        <v>203.45</v>
       </c>
       <c r="G73" t="n">
-        <v>1583670000</v>
+        <v>3798340000</v>
       </c>
       <c r="H73" t="n">
-        <v>8.720000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="I73" t="n">
-        <v>8.82</v>
+        <v>15.64</v>
       </c>
       <c r="K73" t="n">
-        <v>-19.08</v>
+        <v>50.53</v>
       </c>
       <c r="L73" t="n">
-        <v>-52.54</v>
+        <v>-95.78</v>
       </c>
       <c r="M73" t="n">
-        <v>-32.13</v>
+        <v>-25.52</v>
       </c>
       <c r="N73" t="n">
-        <v>35</v>
+        <v>19.69</v>
       </c>
       <c r="O73" t="n">
-        <v>-187.95</v>
+        <v>-2066.55</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="R73" t="n">
-        <v>12.61</v>
+        <v>3.08</v>
       </c>
       <c r="S73" t="n">
-        <v>59.16</v>
+        <v>48.92</v>
       </c>
       <c r="T73" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="U73" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
     </row>
   </sheetData>
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1927.03</v>
+        <v>1945.03</v>
       </c>
       <c r="C2" t="n">
-        <v>55.82</v>
+        <v>56.99</v>
       </c>
       <c r="D2" t="n">
-        <v>55.62</v>
+        <v>56.14</v>
       </c>
       <c r="E2" t="n">
-        <v>6.69</v>
+        <v>6.76</v>
       </c>
       <c r="F2" t="n">
-        <v>67836130000</v>
+        <v>68469780000</v>
       </c>
       <c r="G2" t="n">
-        <v>1541.62</v>
+        <v>1556.02</v>
       </c>
       <c r="H2" t="n">
         <v>2115.29</v>
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9.77</v>
+        <v>8.75</v>
       </c>
       <c r="K2" t="n">
         <v>56.47</v>
@@ -5601,7 +5601,7 @@
         <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>57.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="3">
@@ -5611,22 +5611,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>840</v>
+        <v>832.59</v>
       </c>
       <c r="C3" t="n">
-        <v>49.85</v>
+        <v>47.98</v>
       </c>
       <c r="D3" t="n">
-        <v>28.11</v>
+        <v>27.86</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="F3" t="n">
-        <v>37329830000</v>
+        <v>37000530000</v>
       </c>
       <c r="G3" t="n">
-        <v>672</v>
+        <v>666.0700000000001</v>
       </c>
       <c r="H3" t="n">
         <v>1000.14</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>19.06</v>
+        <v>20.12</v>
       </c>
       <c r="K3" t="n">
         <v>19.67</v>
@@ -5665,7 +5665,7 @@
         <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>861.1</v>
+        <v>851.9</v>
       </c>
       <c r="C4" t="n">
-        <v>55.63</v>
+        <v>54.67</v>
       </c>
       <c r="D4" t="n">
-        <v>76.98</v>
+        <v>76.16</v>
       </c>
       <c r="E4" t="n">
-        <v>9.16</v>
+        <v>9.06</v>
       </c>
       <c r="F4" t="n">
-        <v>26423670000</v>
+        <v>26141360000</v>
       </c>
       <c r="G4" t="n">
-        <v>688.88</v>
+        <v>681.52</v>
       </c>
       <c r="H4" t="n">
         <v>956.4299999999999</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>11.07</v>
+        <v>12.27</v>
       </c>
       <c r="K4" t="n">
         <v>91.59</v>
@@ -5729,7 +5729,7 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60.7</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5855,25 +5855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>675.96</v>
+        <v>681.33</v>
       </c>
       <c r="C2" t="n">
-        <v>56.47</v>
+        <v>57.56</v>
       </c>
       <c r="E2" t="n">
-        <v>33.78</v>
+        <v>34.05</v>
       </c>
       <c r="F2" t="n">
-        <v>172076840000</v>
+        <v>173442170000</v>
       </c>
       <c r="G2" t="n">
-        <v>540.77</v>
+        <v>545.0599999999999</v>
       </c>
       <c r="H2" t="n">
         <v>720.9299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.65</v>
+        <v>5.81</v>
       </c>
       <c r="K2" t="n">
         <v>25.57</v>
@@ -5903,7 +5903,7 @@
         <v>1.59</v>
       </c>
       <c r="T2" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="3">
@@ -5913,22 +5913,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278.6</v>
+        <v>279.4</v>
       </c>
       <c r="C3" t="n">
-        <v>62.5</v>
+        <v>63.05</v>
       </c>
       <c r="D3" t="n">
-        <v>229.17</v>
+        <v>229.83</v>
       </c>
       <c r="E3" t="n">
-        <v>21.41</v>
+        <v>21.47</v>
       </c>
       <c r="F3" t="n">
-        <v>227059010000</v>
+        <v>227715000000</v>
       </c>
       <c r="G3" t="n">
-        <v>222.88</v>
+        <v>223.52</v>
       </c>
       <c r="H3" t="n">
         <v>320.25</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14.95</v>
+        <v>14.62</v>
       </c>
       <c r="K3" t="n">
         <v>31.15</v>
@@ -5967,7 +5967,7 @@
         <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="4">
@@ -5977,25 +5977,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126.2</v>
+        <v>126.15</v>
       </c>
       <c r="C4" t="n">
-        <v>41.1</v>
+        <v>41.07</v>
       </c>
       <c r="E4" t="n">
         <v>6.43</v>
       </c>
       <c r="F4" t="n">
-        <v>20407740000</v>
+        <v>20400460000</v>
       </c>
       <c r="G4" t="n">
-        <v>100.96</v>
+        <v>100.92</v>
       </c>
       <c r="H4" t="n">
         <v>192.67</v>
       </c>
       <c r="J4" t="n">
-        <v>52.67</v>
+        <v>52.73</v>
       </c>
       <c r="K4" t="n">
         <v>25.43</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.75</v>
+        <v>115.31</v>
       </c>
       <c r="C5" t="n">
-        <v>58.77</v>
+        <v>58.28</v>
       </c>
       <c r="D5" t="n">
-        <v>84.06999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="E5" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="F5" t="n">
-        <v>20118200000</v>
+        <v>20040860000</v>
       </c>
       <c r="G5" t="n">
-        <v>92.59999999999999</v>
+        <v>92.25</v>
       </c>
       <c r="H5" t="n">
         <v>120.2</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.84</v>
+        <v>4.24</v>
       </c>
       <c r="K5" t="n">
         <v>11.19</v>
@@ -6089,7 +6089,7 @@
         <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -6099,25 +6099,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.92</v>
+        <v>69.88</v>
       </c>
       <c r="C6" t="n">
-        <v>50.4</v>
+        <v>52.12</v>
       </c>
       <c r="E6" t="n">
-        <v>9.960000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="F6" t="n">
-        <v>14185680000</v>
+        <v>14382250000</v>
       </c>
       <c r="G6" t="n">
-        <v>55.14</v>
+        <v>55.9</v>
       </c>
       <c r="H6" t="n">
         <v>94.37</v>
       </c>
       <c r="J6" t="n">
-        <v>36.93</v>
+        <v>35.05</v>
       </c>
       <c r="K6" t="n">
         <v>38.99</v>
@@ -6144,7 +6144,7 @@
         <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
     </row>
   </sheetData>
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>591</v>
+        <v>611.5</v>
       </c>
       <c r="C2" t="n">
-        <v>73.17</v>
+        <v>75.31</v>
       </c>
       <c r="D2" t="n">
-        <v>55.53</v>
+        <v>57.46</v>
       </c>
       <c r="E2" t="n">
-        <v>16.17</v>
+        <v>16.73</v>
       </c>
       <c r="F2" t="n">
-        <v>469230010000</v>
+        <v>485506180000</v>
       </c>
       <c r="G2" t="n">
-        <v>472.8</v>
+        <v>489.2</v>
       </c>
       <c r="H2" t="n">
         <v>529.8200000000001</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.35</v>
+        <v>-13.36</v>
       </c>
       <c r="K2" t="n">
         <v>11.41</v>
@@ -6324,7 +6324,7 @@
         <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>43.6</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="3">
@@ -6334,22 +6334,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>382.6</v>
+        <v>388.68</v>
       </c>
       <c r="C3" t="n">
-        <v>67.23999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="D3" t="n">
-        <v>72.20999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="E3" t="n">
-        <v>22.07</v>
+        <v>22.42</v>
       </c>
       <c r="F3" t="n">
-        <v>478468490000</v>
+        <v>486071950000</v>
       </c>
       <c r="G3" t="n">
-        <v>306.08</v>
+        <v>310.94</v>
       </c>
       <c r="H3" t="n">
         <v>337.34</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-11.83</v>
+        <v>-13.21</v>
       </c>
       <c r="K3" t="n">
         <v>23.76</v>
@@ -6388,7 +6388,7 @@
         <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="4">
@@ -6398,31 +6398,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>245.98</v>
+        <v>245.33</v>
       </c>
       <c r="C4" t="n">
-        <v>66.36</v>
+        <v>66.17</v>
       </c>
       <c r="D4" t="n">
-        <v>69.54000000000001</v>
+        <v>69.36</v>
       </c>
       <c r="E4" t="n">
-        <v>24.55</v>
+        <v>24.48</v>
       </c>
       <c r="F4" t="n">
-        <v>321317580000</v>
+        <v>320468510000</v>
       </c>
       <c r="G4" t="n">
-        <v>196.78</v>
+        <v>196.26</v>
       </c>
       <c r="H4" t="n">
-        <v>197.06</v>
+        <v>200</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-19.89</v>
+        <v>-18.48</v>
       </c>
       <c r="K4" t="n">
         <v>11.52</v>
@@ -6452,7 +6452,7 @@
         <v>2.03</v>
       </c>
       <c r="T4" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -6462,31 +6462,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>326.9</v>
+        <v>329.95</v>
       </c>
       <c r="C5" t="n">
-        <v>63.89</v>
+        <v>64.55</v>
       </c>
       <c r="D5" t="n">
-        <v>151.76</v>
+        <v>153.17</v>
       </c>
       <c r="E5" t="n">
-        <v>15.78</v>
+        <v>15.93</v>
       </c>
       <c r="F5" t="n">
-        <v>16261170000</v>
+        <v>16412640000</v>
       </c>
       <c r="G5" t="n">
-        <v>261.52</v>
+        <v>263.96</v>
       </c>
       <c r="H5" t="n">
-        <v>351.6</v>
+        <v>353.27</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7.56</v>
+        <v>7.07</v>
       </c>
       <c r="K5" t="n">
         <v>9.51</v>
@@ -6513,10 +6513,10 @@
         <v>99.22</v>
       </c>
       <c r="S5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T5" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="6">
@@ -6526,22 +6526,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>180.94</v>
       </c>
       <c r="C6" t="n">
-        <v>61.45</v>
+        <v>61.04</v>
       </c>
       <c r="D6" t="n">
-        <v>56.7</v>
+        <v>56.37</v>
       </c>
       <c r="E6" t="n">
-        <v>6.62</v>
+        <v>6.58</v>
       </c>
       <c r="F6" t="n">
-        <v>5593570000</v>
+        <v>5560920000</v>
       </c>
       <c r="G6" t="n">
-        <v>145.6</v>
+        <v>144.75</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.54</v>
+        <v>-11.02</v>
       </c>
       <c r="K6" t="n">
         <v>3.32</v>
@@ -6580,7 +6580,7 @@
         <v>2.67</v>
       </c>
       <c r="T6" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="7">
@@ -6590,22 +6590,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.91</v>
+        <v>31.76</v>
       </c>
       <c r="C7" t="n">
-        <v>36.3</v>
+        <v>38.41</v>
       </c>
       <c r="D7" t="n">
-        <v>11.32</v>
+        <v>11.63</v>
       </c>
       <c r="E7" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1822570000</v>
+        <v>1872690000</v>
       </c>
       <c r="G7" t="n">
-        <v>24.73</v>
+        <v>25.41</v>
       </c>
       <c r="H7" t="n">
         <v>43</v>
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>39.11</v>
+        <v>35.39</v>
       </c>
       <c r="K7" t="n">
         <v>-0.5</v>
@@ -6644,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>63.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -6654,22 +6654,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>432.3</v>
+        <v>436.29</v>
       </c>
       <c r="C8" t="n">
-        <v>55.28</v>
+        <v>56.49</v>
       </c>
       <c r="D8" t="n">
-        <v>35.93</v>
+        <v>36.26</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87</v>
+        <v>17.03</v>
       </c>
       <c r="F8" t="n">
-        <v>2242115240000</v>
+        <v>2262809400000</v>
       </c>
       <c r="G8" t="n">
-        <v>345.84</v>
+        <v>349.03</v>
       </c>
       <c r="H8" t="n">
         <v>460.4</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>6.5</v>
+        <v>5.53</v>
       </c>
       <c r="K8" t="n">
         <v>40.49</v>
@@ -6708,7 +6708,7 @@
         <v>1.21</v>
       </c>
       <c r="T8" t="n">
-        <v>59.3</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="9">
@@ -6718,22 +6718,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.40000000000001</v>
+        <v>82.37</v>
       </c>
       <c r="C9" t="n">
-        <v>56.07</v>
+        <v>57.12</v>
       </c>
       <c r="D9" t="n">
-        <v>58.48</v>
+        <v>59.17</v>
       </c>
       <c r="E9" t="n">
-        <v>6.53</v>
+        <v>6.6</v>
       </c>
       <c r="F9" t="n">
-        <v>44641100000</v>
+        <v>45173060000</v>
       </c>
       <c r="G9" t="n">
-        <v>65.12</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>80.7</v>
@@ -6742,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.86</v>
+        <v>-2.03</v>
       </c>
       <c r="K9" t="n">
         <v>3.09</v>
@@ -6772,7 +6772,7 @@
         <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="10">
@@ -6782,25 +6782,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.43</v>
+        <v>121.64</v>
       </c>
       <c r="C10" t="n">
-        <v>57.54</v>
+        <v>57.66</v>
       </c>
       <c r="E10" t="n">
-        <v>11.35</v>
+        <v>11.37</v>
       </c>
       <c r="F10" t="n">
-        <v>610307190000</v>
+        <v>611337530000</v>
       </c>
       <c r="G10" t="n">
-        <v>97.14</v>
+        <v>97.31</v>
       </c>
       <c r="H10" t="n">
         <v>100.81</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.98</v>
+        <v>-17.12</v>
       </c>
       <c r="K10" t="n">
         <v>7.18</v>
@@ -6840,22 +6840,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>269.4</v>
+        <v>272.89</v>
       </c>
       <c r="C11" t="n">
-        <v>55.36</v>
+        <v>56.29</v>
       </c>
       <c r="D11" t="n">
-        <v>125.13</v>
+        <v>126.75</v>
       </c>
       <c r="E11" t="n">
-        <v>18.57</v>
+        <v>18.81</v>
       </c>
       <c r="F11" t="n">
-        <v>30107240000</v>
+        <v>30497270000</v>
       </c>
       <c r="G11" t="n">
-        <v>215.52</v>
+        <v>218.31</v>
       </c>
       <c r="H11" t="n">
         <v>313.83</v>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>16.49</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
         <v>15.48</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
   </sheetData>
@@ -7020,22 +7020,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.63</v>
+        <v>29.13</v>
       </c>
       <c r="C2" t="n">
-        <v>40.54</v>
+        <v>39.66</v>
       </c>
       <c r="D2" t="n">
-        <v>15.63</v>
+        <v>15.37</v>
       </c>
       <c r="E2" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>19165170000</v>
+        <v>18843410000</v>
       </c>
       <c r="G2" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="H2" t="n">
         <v>35.87</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>21.06</v>
+        <v>23.14</v>
       </c>
       <c r="K2" t="n">
         <v>122.68</v>
@@ -7074,7 +7074,7 @@
         <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -7084,28 +7084,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>407.84</v>
+        <v>414.4</v>
       </c>
       <c r="C3" t="n">
-        <v>65.75</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>32.41</v>
+        <v>32.93</v>
       </c>
       <c r="E3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>264325840000</v>
+        <v>268579180000</v>
       </c>
       <c r="G3" t="n">
-        <v>326.27</v>
+        <v>331.52</v>
       </c>
       <c r="H3" t="n">
         <v>496.76</v>
       </c>
       <c r="J3" t="n">
-        <v>21.8</v>
+        <v>19.87</v>
       </c>
       <c r="K3" t="n">
         <v>87.48999999999999</v>
@@ -7132,7 +7132,7 @@
         <v>1.73</v>
       </c>
       <c r="T3" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="4">
@@ -7142,22 +7142,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.52</v>
+        <v>50.06</v>
       </c>
       <c r="C4" t="n">
-        <v>63.2</v>
+        <v>65.56</v>
       </c>
       <c r="D4" t="n">
-        <v>46.52</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="n">
-        <v>64250360000</v>
+        <v>66296250000</v>
       </c>
       <c r="G4" t="n">
-        <v>38.82</v>
+        <v>40.05</v>
       </c>
       <c r="H4" t="n">
         <v>68.59</v>
@@ -7166,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>41.36</v>
+        <v>37.02</v>
       </c>
       <c r="K4" t="n">
         <v>40.64</v>
@@ -7196,7 +7196,7 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>55.9</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -7322,22 +7322,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100.73</v>
+        <v>101</v>
       </c>
       <c r="C2" t="n">
-        <v>45.19</v>
+        <v>45.42</v>
       </c>
       <c r="D2" t="n">
-        <v>59.92</v>
+        <v>60.08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="F2" t="n">
-        <v>103883660000</v>
+        <v>104162110000</v>
       </c>
       <c r="G2" t="n">
-        <v>80.58</v>
+        <v>80.8</v>
       </c>
       <c r="H2" t="n">
         <v>140.76</v>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>39.74</v>
+        <v>39.37</v>
       </c>
       <c r="K2" t="n">
         <v>22.09</v>
@@ -7376,7 +7376,7 @@
         <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="3">
@@ -7386,22 +7386,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230</v>
+        <v>229.91</v>
       </c>
       <c r="C3" t="n">
-        <v>56.99</v>
+        <v>56.93</v>
       </c>
       <c r="D3" t="n">
-        <v>613.8200000000001</v>
+        <v>613.5700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>22.3</v>
+        <v>22.29</v>
       </c>
       <c r="F3" t="n">
-        <v>81870840000</v>
+        <v>81837530000</v>
       </c>
       <c r="G3" t="n">
-        <v>184</v>
+        <v>183.93</v>
       </c>
       <c r="H3" t="n">
         <v>241.25</v>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="K3" t="n">
         <v>32.15</v>
@@ -7440,7 +7440,7 @@
         <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="4">
@@ -7450,22 +7450,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.46</v>
+        <v>41.78</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>55.32</v>
       </c>
       <c r="D4" t="n">
-        <v>77.34</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.99</v>
+        <v>6.03</v>
       </c>
       <c r="F4" t="n">
-        <v>12084580000</v>
+        <v>12177850000</v>
       </c>
       <c r="G4" t="n">
-        <v>33.17</v>
+        <v>33.42</v>
       </c>
       <c r="H4" t="n">
         <v>45.25</v>
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9.140000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="K4" t="n">
         <v>19.44</v>
@@ -7504,7 +7504,7 @@
         <v>1.77</v>
       </c>
       <c r="T4" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="5">
@@ -7514,25 +7514,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.9</v>
+        <v>10.65</v>
       </c>
       <c r="C5" t="n">
-        <v>58.95</v>
+        <v>55.1</v>
       </c>
       <c r="E5" t="n">
-        <v>6.33</v>
+        <v>6.18</v>
       </c>
       <c r="F5" t="n">
-        <v>1583670000</v>
+        <v>1547350000</v>
       </c>
       <c r="G5" t="n">
-        <v>8.720000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="H5" t="n">
         <v>8.82</v>
       </c>
       <c r="J5" t="n">
-        <v>-19.08</v>
+        <v>-17.18</v>
       </c>
       <c r="K5" t="n">
         <v>-52.54</v>
@@ -7562,7 +7562,7 @@
         <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="6">
@@ -7572,25 +7572,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>346.92</v>
+        <v>342.39</v>
       </c>
       <c r="C6" t="n">
-        <v>53.87</v>
+        <v>52.47</v>
       </c>
       <c r="E6" t="n">
-        <v>10.72</v>
+        <v>10.58</v>
       </c>
       <c r="F6" t="n">
-        <v>27903440000</v>
+        <v>27539090000</v>
       </c>
       <c r="G6" t="n">
-        <v>277.54</v>
+        <v>273.91</v>
       </c>
       <c r="H6" t="n">
         <v>399.82</v>
       </c>
       <c r="J6" t="n">
-        <v>15.25</v>
+        <v>16.77</v>
       </c>
       <c r="K6" t="n">
         <v>25.25</v>
@@ -7620,7 +7620,7 @@
         <v>1.59</v>
       </c>
       <c r="T6" t="n">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
     </row>
   </sheetData>
@@ -7746,25 +7746,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.25</v>
+        <v>287.92</v>
       </c>
       <c r="C2" t="n">
-        <v>55.19</v>
+        <v>55.88</v>
       </c>
       <c r="E2" t="n">
-        <v>33.13</v>
+        <v>33.44</v>
       </c>
       <c r="F2" t="n">
-        <v>81137620000</v>
+        <v>81896380000</v>
       </c>
       <c r="G2" t="n">
-        <v>228.2</v>
+        <v>230.34</v>
       </c>
       <c r="H2" t="n">
         <v>279.01</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.19</v>
+        <v>-3.09</v>
       </c>
       <c r="K2" t="n">
         <v>130.37</v>
@@ -7794,7 +7794,7 @@
         <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="3">
@@ -7804,25 +7804,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.91</v>
+        <v>23.97</v>
       </c>
       <c r="C3" t="n">
-        <v>54.9</v>
+        <v>55.03</v>
       </c>
       <c r="E3" t="n">
         <v>1.71</v>
       </c>
       <c r="F3" t="n">
-        <v>4407730000</v>
+        <v>4417930000</v>
       </c>
       <c r="G3" t="n">
-        <v>19.13</v>
+        <v>19.18</v>
       </c>
       <c r="H3" t="n">
         <v>18.65</v>
       </c>
       <c r="J3" t="n">
-        <v>-22</v>
+        <v>-22.19</v>
       </c>
       <c r="K3" t="n">
         <v>7.71</v>
@@ -7862,25 +7862,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.44</v>
+        <v>7.66</v>
       </c>
       <c r="C4" t="n">
-        <v>65.45</v>
+        <v>66.91</v>
       </c>
       <c r="E4" t="n">
-        <v>227.96</v>
+        <v>234.86</v>
       </c>
       <c r="F4" t="n">
-        <v>1326750000</v>
+        <v>1366880000</v>
       </c>
       <c r="G4" t="n">
-        <v>5.95</v>
+        <v>6.13</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.91</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>479.14</v>
@@ -7910,7 +7910,7 @@
         <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -8036,22 +8036,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390.23</v>
+        <v>385.45</v>
       </c>
       <c r="C2" t="n">
-        <v>38.67</v>
+        <v>36.84</v>
       </c>
       <c r="D2" t="n">
-        <v>23.24</v>
+        <v>22.96</v>
       </c>
       <c r="E2" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>2898798110000</v>
+        <v>2863327150000</v>
       </c>
       <c r="G2" t="n">
-        <v>312.18</v>
+        <v>308.36</v>
       </c>
       <c r="H2" t="n">
         <v>559.29</v>
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43.32</v>
+        <v>45.1</v>
       </c>
       <c r="K2" t="n">
         <v>18.3</v>
@@ -8090,7 +8090,7 @@
         <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>63.9</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -8100,22 +8100,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>246.71</v>
+        <v>240.2</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>38.69</v>
       </c>
       <c r="D3" t="n">
-        <v>29.48</v>
+        <v>28.71</v>
       </c>
       <c r="E3" t="n">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="F3" t="n">
-        <v>2653886530000</v>
+        <v>2583857640000</v>
       </c>
       <c r="G3" t="n">
-        <v>197.37</v>
+        <v>192.16</v>
       </c>
       <c r="H3" t="n">
         <v>316.56</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>28.31</v>
+        <v>31.79</v>
       </c>
       <c r="K3" t="n">
         <v>16.61</v>
@@ -8154,7 +8154,7 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>59.6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -8164,22 +8164,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>186.92</v>
+        <v>188.04</v>
       </c>
       <c r="C4" t="n">
-        <v>44.09</v>
+        <v>44.6</v>
       </c>
       <c r="D4" t="n">
-        <v>32.08</v>
+        <v>32.28</v>
       </c>
       <c r="E4" t="n">
-        <v>7.98</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>537590490000</v>
+        <v>540826050000</v>
       </c>
       <c r="G4" t="n">
-        <v>149.54</v>
+        <v>150.43</v>
       </c>
       <c r="H4" t="n">
         <v>255.38</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>36.63</v>
+        <v>35.81</v>
       </c>
       <c r="K4" t="n">
         <v>20.63</v>
@@ -8218,7 +8218,7 @@
         <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>55.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="5">
@@ -8228,25 +8228,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117.32</v>
+        <v>118.93</v>
       </c>
       <c r="C5" t="n">
-        <v>58.03</v>
+        <v>59.04</v>
       </c>
       <c r="E5" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="F5" t="n">
-        <v>64006320000</v>
+        <v>64881960000</v>
       </c>
       <c r="G5" t="n">
-        <v>93.86</v>
+        <v>95.14</v>
       </c>
       <c r="H5" t="n">
         <v>138.91</v>
       </c>
       <c r="J5" t="n">
-        <v>18.4</v>
+        <v>16.8</v>
       </c>
       <c r="K5" t="n">
         <v>111.69</v>
@@ -8276,7 +8276,7 @@
         <v>1.92</v>
       </c>
       <c r="T5" t="n">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="6">
@@ -8286,22 +8286,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>267.74</v>
+        <v>279.22</v>
       </c>
       <c r="C6" t="n">
-        <v>65.84</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>89.33</v>
+        <v>93.16</v>
       </c>
       <c r="E6" t="n">
-        <v>76.75</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>67376880000</v>
+        <v>70265830000</v>
       </c>
       <c r="G6" t="n">
-        <v>214.19</v>
+        <v>223.38</v>
       </c>
       <c r="H6" t="n">
         <v>255.29</v>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.65</v>
+        <v>-8.57</v>
       </c>
       <c r="K6" t="n">
         <v>621.52</v>
@@ -8340,7 +8340,7 @@
         <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="7">
@@ -8350,22 +8350,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>371.07</v>
+        <v>363.82</v>
       </c>
       <c r="C7" t="n">
-        <v>50.88</v>
+        <v>46.11</v>
       </c>
       <c r="D7" t="n">
-        <v>28.31</v>
+        <v>27.75</v>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>10.39</v>
       </c>
       <c r="F7" t="n">
-        <v>4484264480000</v>
+        <v>4396650510000</v>
       </c>
       <c r="G7" t="n">
-        <v>296.86</v>
+        <v>291.06</v>
       </c>
       <c r="H7" t="n">
         <v>433.97</v>
@@ -8374,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>16.95</v>
+        <v>19.28</v>
       </c>
       <c r="K7" t="n">
         <v>22.34</v>
@@ -8404,7 +8404,7 @@
         <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>61.9</v>
+        <v>63.1</v>
       </c>
     </row>
   </sheetData>
@@ -8530,22 +8530,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>145.17</v>
+        <v>148.34</v>
       </c>
       <c r="C2" t="n">
-        <v>54.61</v>
+        <v>58.49</v>
       </c>
       <c r="D2" t="n">
-        <v>25.96</v>
+        <v>26.53</v>
       </c>
       <c r="E2" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="F2" t="n">
-        <v>88570480000</v>
+        <v>90501500000</v>
       </c>
       <c r="G2" t="n">
-        <v>116.14</v>
+        <v>118.67</v>
       </c>
       <c r="H2" t="n">
         <v>157.1</v>
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8.220000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="K2" t="n">
         <v>8.210000000000001</v>
@@ -8584,7 +8584,7 @@
         <v>2.19</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71.23</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>63.21</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>46.8</v>
+        <v>47.13</v>
       </c>
       <c r="E3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="F3" t="n">
-        <v>59162250000</v>
+        <v>59581690000</v>
       </c>
       <c r="G3" t="n">
-        <v>56.98</v>
+        <v>57.39</v>
       </c>
       <c r="H3" t="n">
         <v>76.40000000000001</v>
@@ -8618,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7.26</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
         <v>2.36</v>
@@ -8648,7 +8648,7 @@
         <v>2.03</v>
       </c>
       <c r="T3" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="4">
@@ -8658,22 +8658,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>229.66</v>
+        <v>232.87</v>
       </c>
       <c r="C4" t="n">
-        <v>56.89</v>
+        <v>59.22</v>
       </c>
       <c r="D4" t="n">
-        <v>32.55</v>
+        <v>33.01</v>
       </c>
       <c r="E4" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="F4" t="n">
-        <v>145524780000</v>
+        <v>147555640000</v>
       </c>
       <c r="G4" t="n">
-        <v>183.73</v>
+        <v>186.3</v>
       </c>
       <c r="H4" t="n">
         <v>251.87</v>
@@ -8682,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9.67</v>
+        <v>8.16</v>
       </c>
       <c r="K4" t="n">
         <v>-6.9</v>
@@ -8712,7 +8712,7 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>38.2</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -8838,22 +8838,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.65</v>
+        <v>112.5</v>
       </c>
       <c r="C2" t="n">
-        <v>53.93</v>
+        <v>53.53</v>
       </c>
       <c r="D2" t="n">
-        <v>27.99</v>
+        <v>27.95</v>
       </c>
       <c r="E2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="F2" t="n">
-        <v>26776170000</v>
+        <v>26740520000</v>
       </c>
       <c r="G2" t="n">
-        <v>90.12</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
         <v>152.31</v>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>35.21</v>
+        <v>35.39</v>
       </c>
       <c r="K2" t="n">
         <v>2.71</v>
@@ -8892,7 +8892,7 @@
         <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="3">
@@ -8902,22 +8902,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135.14</v>
+        <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>62.7</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>30.56</v>
+        <v>30.76</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="F3" t="n">
-        <v>3944140000</v>
+        <v>3969350000</v>
       </c>
       <c r="G3" t="n">
-        <v>108.11</v>
+        <v>108.8</v>
       </c>
       <c r="H3" t="n">
         <v>147</v>
@@ -8926,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="K3" t="n">
         <v>-8.970000000000001</v>
@@ -8956,7 +8956,7 @@
         <v>2.13</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="4">
@@ -8966,22 +8966,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.32</v>
+        <v>26.25</v>
       </c>
       <c r="C4" t="n">
-        <v>55.45</v>
+        <v>54.61</v>
       </c>
       <c r="D4" t="n">
-        <v>19.97</v>
+        <v>19.92</v>
       </c>
       <c r="E4" t="n">
         <v>2.81</v>
       </c>
       <c r="F4" t="n">
-        <v>4118319999</v>
+        <v>4106590000</v>
       </c>
       <c r="G4" t="n">
-        <v>21.06</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
         <v>32.2</v>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>22.34</v>
+        <v>22.67</v>
       </c>
       <c r="K4" t="n">
         <v>5.52</v>
@@ -9020,7 +9020,7 @@
         <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
     </row>
   </sheetData>
@@ -9146,22 +9146,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>215.31</v>
+        <v>219.62</v>
       </c>
       <c r="C2" t="n">
-        <v>55.8</v>
+        <v>60.64</v>
       </c>
       <c r="D2" t="n">
-        <v>34.75</v>
+        <v>35.44</v>
       </c>
       <c r="E2" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="F2" t="n">
-        <v>55313140000</v>
+        <v>56420480000</v>
       </c>
       <c r="G2" t="n">
-        <v>172.25</v>
+        <v>175.7</v>
       </c>
       <c r="H2" t="n">
         <v>265.37</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>23.25</v>
+        <v>20.83</v>
       </c>
       <c r="K2" t="n">
         <v>27.65</v>
@@ -9200,7 +9200,7 @@
         <v>1.59</v>
       </c>
       <c r="T2" t="n">
-        <v>57.1</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="3">
@@ -9210,22 +9210,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.42</v>
+        <v>35.94</v>
       </c>
       <c r="C3" t="n">
-        <v>59.86</v>
+        <v>61.85</v>
       </c>
       <c r="D3" t="n">
-        <v>48.13</v>
+        <v>48.84</v>
       </c>
       <c r="E3" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="F3" t="n">
-        <v>9338820000</v>
+        <v>9475920000</v>
       </c>
       <c r="G3" t="n">
-        <v>28.34</v>
+        <v>28.75</v>
       </c>
       <c r="H3" t="n">
         <v>41.56</v>
@@ -9234,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>17.33</v>
+        <v>15.64</v>
       </c>
       <c r="K3" t="n">
         <v>14.57</v>
@@ -9261,7 +9261,7 @@
         <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>48.4</v>
+        <v>47.8</v>
       </c>
     </row>
   </sheetData>
@@ -9397,22 +9397,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.59</v>
+        <v>26.84</v>
       </c>
       <c r="D2" t="n">
-        <v>48.18</v>
+        <v>53.44</v>
       </c>
       <c r="G2" t="n">
-        <v>1280730000</v>
+        <v>1397800000</v>
       </c>
       <c r="H2" t="n">
-        <v>19.67</v>
+        <v>21.47</v>
       </c>
       <c r="I2" t="n">
         <v>45.6</v>
       </c>
       <c r="K2" t="n">
-        <v>85.44</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>69.08</v>
@@ -9433,7 +9433,7 @@
         <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>72.8</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="3">
@@ -9448,25 +9448,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.92</v>
+        <v>69.88</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>52.12</v>
       </c>
       <c r="F3" t="n">
-        <v>9.960000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="G3" t="n">
-        <v>14185680000</v>
+        <v>14382250000</v>
       </c>
       <c r="H3" t="n">
-        <v>55.14</v>
+        <v>55.9</v>
       </c>
       <c r="I3" t="n">
         <v>94.37</v>
       </c>
       <c r="K3" t="n">
-        <v>36.93</v>
+        <v>35.05</v>
       </c>
       <c r="L3" t="n">
         <v>38.99</v>
@@ -9493,7 +9493,7 @@
         <v>1.1</v>
       </c>
       <c r="U3" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="4">
@@ -9508,22 +9508,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.66</v>
+        <v>60.04</v>
       </c>
       <c r="D4" t="n">
-        <v>43.92</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>10032320000</v>
+        <v>10447290000</v>
       </c>
       <c r="H4" t="n">
-        <v>46.13</v>
+        <v>48.03</v>
       </c>
       <c r="I4" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>53.07</v>
+        <v>47</v>
       </c>
       <c r="M4" t="n">
         <v>-173.38</v>
@@ -9544,7 +9544,7 @@
         <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>49.8</v>
+        <v>47.4</v>
       </c>
     </row>
   </sheetData>
@@ -9670,22 +9670,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>402.81</v>
+        <v>403.42</v>
       </c>
       <c r="C2" t="n">
-        <v>42.6</v>
+        <v>43.02</v>
       </c>
       <c r="D2" t="n">
-        <v>32.47</v>
+        <v>32.52</v>
       </c>
       <c r="E2" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="F2" t="n">
-        <v>66864460000</v>
+        <v>66965940000</v>
       </c>
       <c r="G2" t="n">
-        <v>322.25</v>
+        <v>322.74</v>
       </c>
       <c r="H2" t="n">
         <v>509.2</v>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>26.41</v>
+        <v>26.22</v>
       </c>
       <c r="K2" t="n">
         <v>7.36</v>
@@ -9724,7 +9724,7 @@
         <v>1.47</v>
       </c>
       <c r="T2" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="3">
@@ -9734,22 +9734,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.98</v>
+        <v>45.53</v>
       </c>
       <c r="C3" t="n">
-        <v>55.33</v>
+        <v>52.25</v>
       </c>
       <c r="D3" t="n">
-        <v>19.08</v>
+        <v>18.89</v>
       </c>
       <c r="E3" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="F3" t="n">
-        <v>2274200000</v>
+        <v>2252140000</v>
       </c>
       <c r="G3" t="n">
-        <v>36.78</v>
+        <v>36.42</v>
       </c>
       <c r="H3" t="n">
         <v>59</v>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>28.32</v>
+        <v>29.58</v>
       </c>
       <c r="K3" t="n">
         <v>11.04</v>
@@ -9788,7 +9788,7 @@
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>51.6</v>
+        <v>52.3</v>
       </c>
     </row>
   </sheetData>
@@ -9914,22 +9914,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208.35</v>
+        <v>206.22</v>
       </c>
       <c r="C2" t="n">
-        <v>48.17</v>
+        <v>46.48</v>
       </c>
       <c r="D2" t="n">
-        <v>31.91</v>
+        <v>31.58</v>
       </c>
       <c r="E2" t="n">
-        <v>19.89</v>
+        <v>19.69</v>
       </c>
       <c r="F2" t="n">
-        <v>5042064980000</v>
+        <v>4990524030000</v>
       </c>
       <c r="G2" t="n">
-        <v>166.68</v>
+        <v>164.98</v>
       </c>
       <c r="H2" t="n">
         <v>309.93</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>48.75</v>
+        <v>50.29</v>
       </c>
       <c r="K2" t="n">
         <v>85.23</v>
@@ -9968,7 +9968,7 @@
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="3">
@@ -9978,22 +9978,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>521</v>
+        <v>523.5</v>
       </c>
       <c r="C3" t="n">
-        <v>58.87</v>
+        <v>59.2</v>
       </c>
       <c r="D3" t="n">
-        <v>170.99</v>
+        <v>171.81</v>
       </c>
       <c r="E3" t="n">
-        <v>22.68</v>
+        <v>22.79</v>
       </c>
       <c r="F3" t="n">
-        <v>849542910000</v>
+        <v>853619410000</v>
       </c>
       <c r="G3" t="n">
-        <v>416.8</v>
+        <v>418.8</v>
       </c>
       <c r="H3" t="n">
         <v>496.32</v>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.74</v>
+        <v>-5.19</v>
       </c>
       <c r="K3" t="n">
         <v>37.85</v>
@@ -10032,7 +10032,7 @@
         <v>1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="4">
@@ -10042,22 +10042,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>387.6</v>
+        <v>397.83</v>
       </c>
       <c r="C4" t="n">
-        <v>44.57</v>
+        <v>47.53</v>
       </c>
       <c r="D4" t="n">
-        <v>64.52</v>
+        <v>66.23</v>
       </c>
       <c r="E4" t="n">
-        <v>24.44</v>
+        <v>25.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1844038070000</v>
+        <v>1892707580000</v>
       </c>
       <c r="G4" t="n">
-        <v>310.08</v>
+        <v>318.26</v>
       </c>
       <c r="H4" t="n">
         <v>524.1799999999999</v>
@@ -10066,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>35.24</v>
+        <v>31.76</v>
       </c>
       <c r="K4" t="n">
         <v>47.87</v>
@@ -10096,7 +10096,7 @@
         <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>60.8</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="5">
@@ -10106,22 +10106,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>286.92</v>
+        <v>293.06</v>
       </c>
       <c r="C5" t="n">
-        <v>60.73</v>
+        <v>61.73</v>
       </c>
       <c r="D5" t="n">
-        <v>98.05</v>
+        <v>100.14</v>
       </c>
       <c r="E5" t="n">
-        <v>28.79</v>
+        <v>29.41</v>
       </c>
       <c r="F5" t="n">
-        <v>250999010000</v>
+        <v>256368880000</v>
       </c>
       <c r="G5" t="n">
-        <v>229.54</v>
+        <v>234.45</v>
       </c>
       <c r="H5" t="n">
         <v>244.35</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.84</v>
+        <v>-16.62</v>
       </c>
       <c r="K5" t="n">
         <v>27.57</v>
@@ -10160,7 +10160,7 @@
         <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>38</v>
+        <v>37.4</v>
       </c>
     </row>
   </sheetData>
@@ -10286,22 +10286,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>268.7</v>
+        <v>271.38</v>
       </c>
       <c r="C2" t="n">
-        <v>48.62</v>
+        <v>50.07</v>
       </c>
       <c r="D2" t="n">
-        <v>23.33</v>
+        <v>23.57</v>
       </c>
       <c r="E2" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="F2" t="n">
-        <v>97051780000</v>
+        <v>98020190000</v>
       </c>
       <c r="G2" t="n">
-        <v>214.96</v>
+        <v>217.1</v>
       </c>
       <c r="H2" t="n">
         <v>365.11</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>35.88</v>
+        <v>34.54</v>
       </c>
       <c r="K2" t="n">
         <v>23.45</v>
@@ -10340,7 +10340,7 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>58.4</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="3">
@@ -10350,22 +10350,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159.21</v>
+        <v>160.81</v>
       </c>
       <c r="C3" t="n">
-        <v>57.1</v>
+        <v>58.36</v>
       </c>
       <c r="D3" t="n">
-        <v>26.59</v>
+        <v>26.85</v>
       </c>
       <c r="E3" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>53682820000</v>
+        <v>54222310000</v>
       </c>
       <c r="G3" t="n">
-        <v>127.37</v>
+        <v>128.65</v>
       </c>
       <c r="H3" t="n">
         <v>230.29</v>
@@ -10374,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>44.65</v>
+        <v>43.21</v>
       </c>
       <c r="K3" t="n">
         <v>-10</v>
@@ -10404,7 +10404,7 @@
         <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="4">
@@ -10414,25 +10414,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>409.8</v>
+        <v>414.73</v>
       </c>
       <c r="C4" t="n">
-        <v>63.25</v>
+        <v>64.34</v>
       </c>
       <c r="E4" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="F4" t="n">
-        <v>18602880000</v>
+        <v>18826680000</v>
       </c>
       <c r="G4" t="n">
-        <v>327.84</v>
+        <v>331.78</v>
       </c>
       <c r="H4" t="n">
         <v>478.62</v>
       </c>
       <c r="J4" t="n">
-        <v>16.79</v>
+        <v>15.41</v>
       </c>
       <c r="K4" t="n">
         <v>21.64</v>
@@ -10462,7 +10462,7 @@
         <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="5">
@@ -10472,22 +10472,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.66</v>
+        <v>60.04</v>
       </c>
       <c r="C5" t="n">
-        <v>43.92</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>10032320000</v>
+        <v>10447290000</v>
       </c>
       <c r="G5" t="n">
-        <v>46.13</v>
+        <v>48.03</v>
       </c>
       <c r="H5" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>53.07</v>
+        <v>47</v>
       </c>
       <c r="L5" t="n">
         <v>-173.38</v>
@@ -10508,7 +10508,7 @@
         <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>49.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="6">
@@ -10518,25 +10518,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.970000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="C6" t="n">
-        <v>42.8</v>
+        <v>45.61</v>
       </c>
       <c r="E6" t="n">
-        <v>195.13</v>
+        <v>203.45</v>
       </c>
       <c r="F6" t="n">
-        <v>3643120000</v>
+        <v>3798340000</v>
       </c>
       <c r="G6" t="n">
-        <v>7.98</v>
+        <v>8.31</v>
       </c>
       <c r="H6" t="n">
         <v>15.64</v>
       </c>
       <c r="J6" t="n">
-        <v>56.87</v>
+        <v>50.53</v>
       </c>
       <c r="K6" t="n">
         <v>-95.78</v>
@@ -10566,7 +10566,7 @@
         <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="7">
@@ -10576,22 +10576,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.59</v>
+        <v>26.84</v>
       </c>
       <c r="C7" t="n">
-        <v>48.18</v>
+        <v>53.44</v>
       </c>
       <c r="F7" t="n">
-        <v>1280730000</v>
+        <v>1397800000</v>
       </c>
       <c r="G7" t="n">
-        <v>19.67</v>
+        <v>21.47</v>
       </c>
       <c r="H7" t="n">
         <v>45.6</v>
       </c>
       <c r="J7" t="n">
-        <v>85.44</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>69.08</v>
@@ -10612,7 +10612,7 @@
         <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>72.8</v>
+        <v>67.8</v>
       </c>
     </row>
   </sheetData>
@@ -10738,22 +10738,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>168.71</v>
+        <v>167.95</v>
       </c>
       <c r="C2" t="n">
-        <v>58.9</v>
+        <v>58.35</v>
       </c>
       <c r="D2" t="n">
-        <v>57.77</v>
+        <v>57.51</v>
       </c>
       <c r="E2" t="n">
-        <v>21.88</v>
+        <v>21.78</v>
       </c>
       <c r="F2" t="n">
-        <v>212440090000</v>
+        <v>211483080000</v>
       </c>
       <c r="G2" t="n">
-        <v>134.97</v>
+        <v>134.36</v>
       </c>
       <c r="H2" t="n">
         <v>189.42</v>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12.28</v>
+        <v>12.78</v>
       </c>
       <c r="K2" t="n">
         <v>35.13</v>
@@ -10792,7 +10792,7 @@
         <v>1.12</v>
       </c>
       <c r="T2" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="3">
@@ -10802,22 +10802,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>246.83</v>
+        <v>258.58</v>
       </c>
       <c r="C3" t="n">
-        <v>59.61</v>
+        <v>62.46</v>
       </c>
       <c r="D3" t="n">
-        <v>99.54000000000001</v>
+        <v>104.27</v>
       </c>
       <c r="E3" t="n">
-        <v>34.48</v>
+        <v>36.12</v>
       </c>
       <c r="F3" t="n">
-        <v>46028340000</v>
+        <v>48218520000</v>
       </c>
       <c r="G3" t="n">
-        <v>197.46</v>
+        <v>206.86</v>
       </c>
       <c r="H3" t="n">
         <v>266.44</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7.94</v>
+        <v>3.04</v>
       </c>
       <c r="K3" t="n">
         <v>157.02</v>
@@ -10856,7 +10856,7 @@
         <v>1.15</v>
       </c>
       <c r="T3" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="4">
@@ -10866,22 +10866,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>372.45</v>
+        <v>384.88</v>
       </c>
       <c r="C4" t="n">
-        <v>63.54</v>
+        <v>65.42</v>
       </c>
       <c r="D4" t="n">
-        <v>251.04</v>
+        <v>259.42</v>
       </c>
       <c r="E4" t="n">
-        <v>63.75</v>
+        <v>65.88</v>
       </c>
       <c r="F4" t="n">
-        <v>63840890000</v>
+        <v>65970640000</v>
       </c>
       <c r="G4" t="n">
-        <v>297.96</v>
+        <v>307.9</v>
       </c>
       <c r="H4" t="n">
         <v>253.06</v>
@@ -10890,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-32.06</v>
+        <v>-34.25</v>
       </c>
       <c r="K4" t="n">
         <v>93.40000000000001</v>
@@ -10920,7 +10920,7 @@
         <v>1.81</v>
       </c>
       <c r="T4" t="n">
-        <v>56.7</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="5">
@@ -10930,22 +10930,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>388.65</v>
+        <v>391.17</v>
       </c>
       <c r="C5" t="n">
-        <v>53.12</v>
+        <v>53.59</v>
       </c>
       <c r="D5" t="n">
-        <v>185.55</v>
+        <v>186.75</v>
       </c>
       <c r="E5" t="n">
-        <v>11.52</v>
+        <v>11.59</v>
       </c>
       <c r="F5" t="n">
-        <v>76035220000</v>
+        <v>76527260000</v>
       </c>
       <c r="G5" t="n">
-        <v>310.92</v>
+        <v>312.94</v>
       </c>
       <c r="H5" t="n">
         <v>388.09</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.14</v>
+        <v>-0.79</v>
       </c>
       <c r="K5" t="n">
         <v>20.55</v>
@@ -10984,7 +10984,7 @@
         <v>1.65</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="6">
@@ -10994,22 +10994,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>882</v>
+        <v>877.04</v>
       </c>
       <c r="C6" t="n">
-        <v>48.31</v>
+        <v>47.9</v>
       </c>
       <c r="D6" t="n">
-        <v>163.69</v>
+        <v>162.77</v>
       </c>
       <c r="E6" t="n">
-        <v>27.58</v>
+        <v>27.42</v>
       </c>
       <c r="F6" t="n">
-        <v>68619600000</v>
+        <v>68233710000</v>
       </c>
       <c r="G6" t="n">
-        <v>705.6</v>
+        <v>701.63</v>
       </c>
       <c r="H6" t="n">
         <v>1132.81</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>28.44</v>
+        <v>29.16</v>
       </c>
       <c r="K6" t="n">
         <v>90.12</v>
@@ -11048,7 +11048,7 @@
         <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
     </row>
   </sheetData>
@@ -11174,22 +11174,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1053.32</v>
+        <v>1044.82</v>
       </c>
       <c r="C2" t="n">
-        <v>62.28</v>
+        <v>61.83</v>
       </c>
       <c r="D2" t="n">
-        <v>49.73</v>
+        <v>49.33</v>
       </c>
       <c r="E2" t="n">
-        <v>20.44</v>
+        <v>20.27</v>
       </c>
       <c r="F2" t="n">
-        <v>1187867070000</v>
+        <v>1178278580000</v>
       </c>
       <c r="G2" t="n">
-        <v>842.66</v>
+        <v>835.86</v>
       </c>
       <c r="H2" t="n">
         <v>954.52</v>
@@ -11198,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-9.380000000000001</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>196.29</v>
@@ -11228,7 +11228,7 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -11238,22 +11238,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>693.5700000000001</v>
+        <v>727.98</v>
       </c>
       <c r="C3" t="n">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>41.4</v>
+        <v>43.46</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3</v>
+        <v>21.31</v>
       </c>
       <c r="F3" t="n">
-        <v>239059460000</v>
+        <v>250921690000</v>
       </c>
       <c r="G3" t="n">
-        <v>554.86</v>
+        <v>582.38</v>
       </c>
       <c r="H3" t="n">
         <v>560</v>
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.26</v>
+        <v>-23.07</v>
       </c>
       <c r="K3" t="n">
         <v>45.47</v>
@@ -11292,7 +11292,7 @@
         <v>1.72</v>
       </c>
       <c r="T3" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="4">
@@ -11302,22 +11302,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1054.9</v>
+        <v>1081.11</v>
       </c>
       <c r="C4" t="n">
-        <v>73.15000000000001</v>
+        <v>74.63</v>
       </c>
       <c r="D4" t="n">
-        <v>100.13</v>
+        <v>102.62</v>
       </c>
       <c r="E4" t="n">
-        <v>21.48</v>
+        <v>22.02</v>
       </c>
       <c r="F4" t="n">
-        <v>236539170000</v>
+        <v>242416200000</v>
       </c>
       <c r="G4" t="n">
-        <v>843.92</v>
+        <v>864.89</v>
       </c>
       <c r="H4" t="n">
         <v>903.55</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-14.35</v>
+        <v>-16.42</v>
       </c>
       <c r="K4" t="n">
         <v>44.07</v>
@@ -11356,7 +11356,7 @@
         <v>1.59</v>
       </c>
       <c r="T4" t="n">
-        <v>43.3</v>
+        <v>42.7</v>
       </c>
     </row>
   </sheetData>
@@ -11482,22 +11482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>191.2</v>
+        <v>189.44</v>
       </c>
       <c r="C2" t="n">
-        <v>54.32</v>
+        <v>51.83</v>
       </c>
       <c r="D2" t="n">
-        <v>50.57</v>
+        <v>50.11</v>
       </c>
       <c r="E2" t="n">
-        <v>10.47</v>
+        <v>10.37</v>
       </c>
       <c r="F2" t="n">
-        <v>67188830000</v>
+        <v>66569800000</v>
       </c>
       <c r="G2" t="n">
-        <v>152.96</v>
+        <v>151.55</v>
       </c>
       <c r="H2" t="n">
         <v>219.17</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>14.63</v>
+        <v>15.69</v>
       </c>
       <c r="K2" t="n">
         <v>16.16</v>
@@ -11536,7 +11536,7 @@
         <v>1.61</v>
       </c>
       <c r="T2" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="3">
@@ -11546,22 +11546,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1096.5</v>
+        <v>1088.51</v>
       </c>
       <c r="C3" t="n">
-        <v>60.1</v>
+        <v>57.23</v>
       </c>
       <c r="D3" t="n">
-        <v>75.83</v>
+        <v>75.28</v>
       </c>
       <c r="E3" t="n">
-        <v>11.46</v>
+        <v>11.38</v>
       </c>
       <c r="F3" t="n">
-        <v>108141490000</v>
+        <v>107353480000</v>
       </c>
       <c r="G3" t="n">
-        <v>877.2</v>
+        <v>870.8099999999999</v>
       </c>
       <c r="H3" t="n">
         <v>1204.61</v>
@@ -11570,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9.859999999999999</v>
+        <v>10.67</v>
       </c>
       <c r="K3" t="n">
         <v>9.84</v>
@@ -11600,7 +11600,7 @@
         <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>41.2</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="4">
@@ -11610,25 +11610,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.9</v>
+        <v>45.95</v>
       </c>
       <c r="C4" t="n">
-        <v>57.96</v>
+        <v>56.32</v>
       </c>
       <c r="E4" t="n">
-        <v>37.71</v>
+        <v>36.94</v>
       </c>
       <c r="F4" t="n">
-        <v>13402340000</v>
+        <v>13131110000</v>
       </c>
       <c r="G4" t="n">
-        <v>37.52</v>
+        <v>36.76</v>
       </c>
       <c r="H4" t="n">
         <v>72.92</v>
       </c>
       <c r="J4" t="n">
-        <v>55.48</v>
+        <v>58.69</v>
       </c>
       <c r="K4" t="n">
         <v>139.29</v>
@@ -11658,7 +11658,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="5">
@@ -11668,28 +11668,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.79</v>
+        <v>128.36</v>
       </c>
       <c r="C5" t="n">
-        <v>54.85</v>
+        <v>56.02</v>
       </c>
       <c r="D5" t="n">
-        <v>140.32</v>
+        <v>140.95</v>
       </c>
       <c r="E5" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="F5" t="n">
-        <v>38020680000</v>
+        <v>38190090000</v>
       </c>
       <c r="G5" t="n">
-        <v>102.23</v>
+        <v>102.69</v>
       </c>
       <c r="H5" t="n">
         <v>131.55</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.49</v>
       </c>
       <c r="K5" t="n">
         <v>21.58</v>
@@ -11716,7 +11716,7 @@
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -11842,22 +11842,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>302.49</v>
+        <v>315.26</v>
       </c>
       <c r="C2" t="n">
-        <v>45.34</v>
+        <v>50.53</v>
       </c>
       <c r="D2" t="n">
-        <v>75.94</v>
+        <v>79.14</v>
       </c>
       <c r="E2" t="n">
-        <v>10.72</v>
+        <v>11.17</v>
       </c>
       <c r="F2" t="n">
-        <v>116189080000</v>
+        <v>121093920000</v>
       </c>
       <c r="G2" t="n">
-        <v>241.99</v>
+        <v>252.21</v>
       </c>
       <c r="H2" t="n">
         <v>380.63</v>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25.83</v>
+        <v>20.74</v>
       </c>
       <c r="K2" t="n">
         <v>30.13</v>
@@ -11896,7 +11896,7 @@
         <v>1.58</v>
       </c>
       <c r="T2" t="n">
-        <v>55.6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -11906,22 +11906,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>291.96</v>
+        <v>293.24</v>
       </c>
       <c r="C3" t="n">
-        <v>56.71</v>
+        <v>57.12</v>
       </c>
       <c r="D3" t="n">
-        <v>130.43</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="F3" t="n">
-        <v>15420090000</v>
+        <v>15487700000</v>
       </c>
       <c r="G3" t="n">
-        <v>233.57</v>
+        <v>234.59</v>
       </c>
       <c r="H3" t="n">
         <v>351.75</v>
@@ -11930,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20.48</v>
+        <v>19.95</v>
       </c>
       <c r="K3" t="n">
         <v>47.47</v>
@@ -11960,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="4">
@@ -11970,22 +11970,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>130.66</v>
+        <v>135.8</v>
       </c>
       <c r="C4" t="n">
-        <v>51.83</v>
+        <v>56.12</v>
       </c>
       <c r="D4" t="n">
-        <v>91.91</v>
+        <v>95.53</v>
       </c>
       <c r="E4" t="n">
-        <v>6.62</v>
+        <v>6.88</v>
       </c>
       <c r="F4" t="n">
-        <v>10702580000</v>
+        <v>11123610000</v>
       </c>
       <c r="G4" t="n">
-        <v>104.53</v>
+        <v>108.64</v>
       </c>
       <c r="H4" t="n">
         <v>149.75</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14.61</v>
+        <v>10.27</v>
       </c>
       <c r="K4" t="n">
         <v>54.3</v>
@@ -12024,7 +12024,7 @@
         <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
     </row>
   </sheetData>
@@ -12150,22 +12150,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>727.84</v>
+        <v>717.0700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>55.63</v>
+        <v>53.21</v>
       </c>
       <c r="D2" t="n">
-        <v>99.84999999999999</v>
+        <v>98.38</v>
       </c>
       <c r="E2" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
       <c r="F2" t="n">
-        <v>109219180000</v>
+        <v>107603630000</v>
       </c>
       <c r="G2" t="n">
-        <v>582.27</v>
+        <v>573.66</v>
       </c>
       <c r="H2" t="n">
         <v>802.79</v>
@@ -12174,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10.3</v>
+        <v>11.95</v>
       </c>
       <c r="K2" t="n">
         <v>26.33</v>
@@ -12204,7 +12204,7 @@
         <v>1.65</v>
       </c>
       <c r="T2" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="3">
@@ -12214,31 +12214,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>992.3</v>
+        <v>1016.18</v>
       </c>
       <c r="C3" t="n">
-        <v>52.23</v>
+        <v>55.58</v>
       </c>
       <c r="D3" t="n">
-        <v>28.91</v>
+        <v>29.61</v>
       </c>
       <c r="E3" t="n">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="F3" t="n">
-        <v>266650860000</v>
+        <v>273069240000</v>
       </c>
       <c r="G3" t="n">
-        <v>793.84</v>
+        <v>812.9400000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1240.22</v>
+        <v>1227.4</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>24.98</v>
+        <v>20.79</v>
       </c>
       <c r="K3" t="n">
         <v>15.98</v>
@@ -12265,10 +12265,10 @@
         <v>78.51000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="T3" t="n">
-        <v>57.1</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="4">
@@ -12278,22 +12278,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>171.17</v>
       </c>
       <c r="C4" t="n">
-        <v>56.79</v>
+        <v>57.82</v>
       </c>
       <c r="D4" t="n">
-        <v>57.17</v>
+        <v>57.56</v>
       </c>
       <c r="E4" t="n">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="F4" t="n">
-        <v>27492480000</v>
+        <v>27681460000</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>136.94</v>
       </c>
       <c r="H4" t="n">
         <v>194.67</v>
@@ -12302,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14.51</v>
+        <v>13.73</v>
       </c>
       <c r="K4" t="n">
         <v>53.47</v>
@@ -12332,7 +12332,7 @@
         <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="5">
@@ -12342,22 +12342,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>296.28</v>
+        <v>299.18</v>
       </c>
       <c r="C5" t="n">
-        <v>54.61</v>
+        <v>55.59</v>
       </c>
       <c r="D5" t="n">
-        <v>57.9</v>
+        <v>58.47</v>
       </c>
       <c r="E5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>10793960000</v>
+        <v>10899690000</v>
       </c>
       <c r="G5" t="n">
-        <v>237.02</v>
+        <v>239.34</v>
       </c>
       <c r="H5" t="n">
         <v>289.17</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.4</v>
+        <v>-3.35</v>
       </c>
       <c r="K5" t="n">
         <v>6.45</v>
@@ -12396,7 +12396,7 @@
         <v>1.86</v>
       </c>
       <c r="T5" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
     </row>
   </sheetData>
@@ -12522,22 +12522,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>412.3</v>
+        <v>414.93</v>
       </c>
       <c r="C2" t="n">
-        <v>54.89</v>
+        <v>55.85</v>
       </c>
       <c r="D2" t="n">
-        <v>40.31</v>
+        <v>40.56</v>
       </c>
       <c r="E2" t="n">
-        <v>5.61</v>
+        <v>5.65</v>
       </c>
       <c r="F2" t="n">
-        <v>160096080000</v>
+        <v>161117310000</v>
       </c>
       <c r="G2" t="n">
-        <v>329.84</v>
+        <v>331.94</v>
       </c>
       <c r="H2" t="n">
         <v>463.71</v>
@@ -12546,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12.47</v>
+        <v>11.76</v>
       </c>
       <c r="K2" t="n">
         <v>16.84</v>
@@ -12576,7 +12576,7 @@
         <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
